--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -1130,58 +1130,133 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
+          <t>36日</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>園田学園大学</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>経営学部　ビジネス学科</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>5名／5名を超える場合は要相談</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>日本語要件の記載なし</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>90%以上</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ期　9月28日（月）～10月7日（水）
+Ⅱ期　11月24日（火）～12月9日（水）
+Ⅲ期　1月25日（月）～2月3日（水）
+Ⅳ期　2月15日（月）～3月2日（火）</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ期　10月18日（日）10：00
+Ⅱ期　12月20日（日）10：00
+Ⅲ期　2月12日（金）10：00
+Ⅳ期　3月9日（火）10：00</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ期　10月23日（金）
+Ⅱ期　12月24日（木）
+Ⅲ期　2月19日（金）
+Ⅳ期　3月12日（金）</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>書類
+面接(10分　100点)
+小論文（10分　100点）</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
           <t>43日</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科・経済学部 経済学科・／システム工学部 システム工学科</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>9/14(月)～10/14(水)</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>10/24（土）
 集合時間:12:30
 試験時間:13:00</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>11/1（日）
 10:00～</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>（１次）入学金の納入と手続き書類の提出
 11/2（月）～12/1（火）消印有効
@@ -1189,7 +1264,7 @@
 11/2（月）～12/17（木）</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>エントリーシートに基づく面接
 200点
@@ -1197,46 +1272,46 @@
 しかし、入学試験の結果において、大学の授業に支障があると判断した場合、不合格の可能性あり。</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>44日</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>国際日本・建築&amp;芸術・現代社会・経営／／大手前短期大学／ライフデザイン総合</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>N2以上、NAT-TEST2級以上、J-TEST(A-Cレベル600点以上)、JPT 525点以上のいずれか。</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/10/1(木)～10/15(木)
 B日程：2026/12/14(月)～2027/1/12(火)
@@ -1244,7 +1319,7 @@
 ※消印有効</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>A日程：11/5(木)
 B日程：1/27(水)
@@ -1252,14 +1327,14 @@
 ※試験会場はすべて、西宮夙川キャンパス</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>A日程：11/19(木)
 B日程：2/11(木・祝)
 C日程：3/4(木)</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>入学金納入期日：
 A日程：2025/12/7(月)
@@ -1272,7 +1347,7 @@
 ※詳細は募集要項に記載あり</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>大学
 ①筆記試験 10:00～11:00
@@ -1286,213 +1361,213 @@
 ②個人面接(約15分)</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>45日</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>現代社会学科・放送・メディア映像学科・人間生活学科／（新）デジタルインテリジェンス学科（仮称）</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>各学科／1名／※新学科のみ未定</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>N2以上取得もしくはEJU270点以上</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>前期:9/7(月)～10/16(金)
 後期:2/1(月)～2/15(月)
 ※必着</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>前期:10/24(土)
 後期:2/19(金)</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>前期:11/2(月)
 後期:2/25(木)</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>前期:11/19(木)
 後期:3/4(木)</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>面接（15分）
 ※読み上げ小テスト含む</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>69日</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>情報学部　情報デザイン学科/グローバル学部　グローバル学科/心理学部　心理学科（神戸山手キャンパス）／教育学部　教育福祉学科/経営学部　経営学科（尼崎キャンパス）</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格している者</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>202610月6日（火）～11月9日（月）
 締切日消印有効</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>11月21日（土）</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>12月1日（火）</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>1次手続き入学金20万円　12月17日（木）
 2次手続き授業料等　2027年1月21日（木）</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>個人面接を実施し、出願書類及び指定校推薦書とあわせて総合判定の上、合否を判定します。
 試験は、日本語による個人面接（20分程度）を、尼崎キャンパスにて対面で行います。</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>70日</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>人文学科、管理栄養学科</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>前期　11/1～11/10
 後期　2/3～2/13</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>前期　11/21
 後期　2/22</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>前期　12/1
 後期　3/3</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>前期：入学金納入→12/11
 前期授業料等納入→6/14
@@ -1500,194 +1575,194 @@
 前期授業料等納入→6/15</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>面接
 （推薦書・志望理由書）を参考にする</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>70日</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>N2以上またはEJU「日本語（記述問題を含む）」230点以上の者(聴読解及び読解で各100点以上、記述30点以上)。</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>2026年11月1日（日）～11月10日（火）
 締切日必着（郵送に限ります。速達　簡易書留で送付します）</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>2026年11月21日（土）
 口頭試問:13:00～</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>2026年12月7日（月）
 13：00～</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>入学金・春学期分学費・諸会費の納付期間2026年12月7日（月）～2027年1月29日（金）</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>日本語による口頭試問　配点100点</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>71日</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>国際学部　日本学科（留学生対象）</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>N2程度の日本語能力を有する者</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>2026/11/2(月)～11/11(水)
 ※必着</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>面接：
 2026/11/20(金)
 ※学校長からの推薦書・調査書及び課題論文をもとに「書類審査」・「面接」により選抜します。</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>2026/12/1(火)
 ※「選考結果通知書」は学校宛てに郵送します。
 本人へは、出願時に登録していただくPost@net のマイページから発表します。</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>【第1次】2026/12/15(水)…入学金
 【第2次】2026/1/20(火)…春学期分納付金と入学手続書類＜必着＞</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>推薦書・調査書及び課題論文をもとに
 「書類審査」・「面接」により選抜</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>72日</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>1期：11月2日(月)～11月12日(木)
 Ⅱ期：12月1日(火)～12月16日(水)
@@ -1696,7 +1771,7 @@
 Ⅴ期：2月24日(水)～3月11日(木)</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月14日(土)
 Ⅱ期：12月19日(土)
@@ -1705,7 +1780,7 @@
 Ⅴ期：3月13日(土)</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月18日(水)
 Ⅱ期：12月23日(水)
@@ -1714,7 +1789,7 @@
 Ⅴ期：3月18日(木)</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月26日(木)
 Ⅱ期：1月7日(木)
@@ -1723,56 +1798,56 @@
 Ⅴ期：3月26日(金)</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>・書類審査
 ・個人面接(日本語の口頭試問含むオンライン試験)</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>87日</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者、または、EJU(日本語/記述除く)200点以上の者。</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>85%以上</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年11月9日(月)～11月27日(金)
 (WEB出願は24日の午後5時まで)
@@ -1783,21 +1858,21 @@
 いずれも必着締め切り</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月5日(土)
 Ⅱ期：2027年2月7日(日)
 Ⅲ期：2027年2月26日(金)</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月11日(金)
 Ⅱ期：2027年2月12日(金)
 Ⅲ期：2027年3月5日(金)</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2027年1月13日(水)
 Ⅱ期：2027年2月26日(金)
@@ -1805,56 +1880,56 @@
 必着締め切り</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>①出願書類審査(志望理由書、在籍校での成績及び出席率、推薦書を含む)
 ②面接試験(15分)…集団面接</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>90日</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>経済経営学科、国際文化ビジネス・観光学科</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>N2相当であるもの（※N2相当は下記いずれかの基準）</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 【前期】
@@ -1867,21 +1942,21 @@
 窓口の場合は16:00まで</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/13
 後期：2/22</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/24
 後期：3/4</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期
@@ -1892,74 +1967,74 @@
 （第二次）〃</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>書類審査
 本学独自の日本語能力試験
 面接</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>100日</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>国際教養学部 英語・国際文化学科、／社会学部 社会学科/社会福祉学科(※現：ソーシャルデザイン学科で2027年4月に社会福祉学科に名称変更構想中)、／法学部 法律学科、経済学部 経済学科、経営学部 経営学科、工学部 工学科</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>N2レベル以上の者、またはEJUの日本語科目(読解、聴解及び聴読解)の得点が220点以上の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>2026年12月1日(火)～12月10日(木)
 ※入学検定料は締め切り12/11(金)13時振込完了
 締切日当日消印有効</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>2026/12/19（土）</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>2026/12/24（木）</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>2026年12月24日(木)～
 2027年2月12日(金)
@@ -1967,7 +2042,7 @@
 入学申込金、春学期授業料一括納入</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>・面接
 ・小論文
@@ -1975,232 +2050,153 @@
 (EJUの成績確認書またはN２以上の成績証明書)/工学部工学科のみEJUの数学コース2及び理科の成績確認書も</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>15日</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>追手門学院大学（パートナー校制度）</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>国際学部 国際学科 グローバルスタディーズ専攻</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr"/>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>【前期】2026年9月10日（木）～2026年9月16日（水）
 【後期】2026年12月18日（金）～2027年1月12日（火）
 ※当日消印有効</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>前期：2026年10月3日（土）
 後期：2027年1月28日（木）</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>【前期】2026年10月9日（金）
 【後期】2027年2月18日（木）</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>【前期】2026年11月9日（月）
 【後期】2027年2月26日（金）</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>筆記試験（日本語読解・小論文）
 面接（日本語・英語）</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
-        <is>
-          <t>日本語(N3以上)は満たすが、英語スコア(TOEFL iBT74 / IELTS5.5 / TOEIC800 / Duolingo100)も別途必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>日语（N3以上）你够，但还另外要求英语成绩（TOEFL iBT74 / IELTS5.5 / TOEIC800 / Duolingo100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>31日</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>京都外国語大学</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>外国語学部　日本語学科／国際貢献学部　グローバルスタディーズ学科・グローバル観光学科</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>3名／(１学科につき　1名)</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>N１：110点以上での合格</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>A日程：2026/9/24(木)～10/2(金)
 B日程：2026/12/8(火)～12/12(土)</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>A日程：2026/10/23(金)
 B日程：2026/12/19(土)</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>A日程：2026/11/1(日)
 B日程：2026/12/25(金)</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>A日程：2026/11/13(金)
 B日程：2027/1/15(金)</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>・書類選考　
 ・個人面接(15分 オンライン)
 ※面接は外国語学部と国際貢献学部グローバル観光学科は【日本語】で、グローバルスタディーズ学科は【英語】で面接を行う。</t>
         </is>
       </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>日本語学科は N1 110点以上で不可。グローバルスタディーズ／グローバル観光学科なら N2 100点以上で可</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>36日</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>園田学園大学</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>経営学部　ビジネス学科</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>5名／5名を超える場合は要相談</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>日本語要件の記載なし</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>90%以上</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Ⅰ期　9月28日（月）～10月7日（水）
-Ⅱ期　11月24日（火）～12月9日（水）
-Ⅲ期　1月25日（月）～2月3日（水）
-Ⅳ期　2月15日（月）～3月2日（火）</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Ⅰ期　10月18日（日）10：00
-Ⅱ期　12月20日（日）10：00
-Ⅲ期　2月12日（金）10：00
-Ⅳ期　3月9日（火）10：00</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>Ⅰ期　10月23日（金）
-Ⅱ期　12月24日（木）
-Ⅲ期　2月19日（金）
-Ⅳ期　3月12日（金）</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>書類
-面接(10分　100点)
-小論文（10分　100点）</t>
-        </is>
-      </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>「日本語教育の参照枠 B2 以上」が条件。N2 111点が B2 判定になるか要確認</t>
+          <t>日本語学科要 N1 110 分以上，报不了。グローバルスタディーズ／グローバル観光学科用 N2 100 分以上可以报</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2294,7 @@
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>条件は N2 で可。ただし出願期間欄が 2025 年の日付のまま＝更新漏れの可能性</t>
+          <t>条件上 N2 可以。但报名期间栏还是 2025 年的日期，可能是漏更新了</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2338,7 @@
       <c r="M23" s="9" t="inlineStr"/>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>リスト「編集中」。条件・日程とも未記載</t>
+          <t>名单上标着「編集中」，条件和日程都还没写</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2431,7 @@
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>N2は112点以上が必要。111点で1点不足（EJU220/JPT525/J.TEST C級600でも可）</t>
+          <t>要求 N2 112 分以上，你 111 分差 1 分（EJU220／JPT525／J.TEST C级600 也可以替代）</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2509,7 @@
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
-          <t>EJU必須（日本語230点、数学コース2も受験要）。JLPT不可</t>
+          <t>必须有 EJU（日语230分，还要考数学课程2）。不认 JLPT</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2585,7 @@
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>女子大学（本人の除外指定）</t>
+          <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2675,7 @@
       </c>
       <c r="N27" s="14" t="inlineStr">
         <is>
-          <t>女子大学（本人の除外指定）</t>
+          <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2750,7 @@
       </c>
       <c r="N28" s="14" t="inlineStr">
         <is>
-          <t>EJU必須（日本語200点）。JLPT不可</t>
+          <t>必须有 EJU（日语200分）。不认 JLPT</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2829,7 @@
       </c>
       <c r="N29" s="14" t="inlineStr">
         <is>
-          <t>EJU必須（日本語300点＋総合科目100点＋総得点400点）。JLPT不可</t>
+          <t>必须有 EJU（日语300分＋综合科目100分＋总分400分）。不认 JLPT</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2904,7 @@
       </c>
       <c r="N30" s="14" t="inlineStr">
         <is>
-          <t>EJU必須（日本語240点）。JLPT不可</t>
+          <t>必须有 EJU（日语240分）。不认 JLPT</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2976,7 @@
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
-          <t>中国国籍以外が条件。該当しない</t>
+          <t>要求中国籍以外，你不符合</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3062,7 @@
       </c>
       <c r="N32" s="14" t="inlineStr">
         <is>
-          <t>短期大学（本人の除外指定）</t>
+          <t>短期大学（你指定排除）</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3167,7 @@
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
-          <t>女子大学（本人の除外指定）</t>
+          <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3258,7 @@
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>短期大学（本人の除外指定）</t>
+          <t>短期大学（你指定排除）</t>
         </is>
       </c>
     </row>
@@ -3488,15 +3484,38 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
+          <t>園田学園大学</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>5名／5名を超える場合は要相談</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>①授業時間600時間を満たした者かつ、日本語教育の参照枠におけるB2以上の日本語能力を有する者
+②出席率90％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>①日本国籍を有しない者
 ②下記（1）～（3）のいずれかを満たす者
@@ -3512,23 +3531,23 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>【大学・短大共通条件↓】
 出席率90%以上
@@ -3554,23 +3573,23 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>各学科／1名／※新学科のみ未定</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>出願資格：次の各項のすべてに該当する者
 ①貴校の校長が推薦し、かつ本学を専願とする者
@@ -3592,23 +3611,23 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>出願資格
 外国籍を有する者で、（1）出願資格のいずれかに該当し、かつ（2）出願条件と（3）（4）を満たし、本学を専願とする者に出願資格があります。
@@ -3628,23 +3647,23 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>【人文学科】
 １～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
@@ -3671,23 +3690,23 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>①外国の国籍を有し、外国において学校教育における12年の課程を修了した者、もしくは2027年3月までに修了見込みの者
 ※12年の課程のうち、日本の高等学校での在籍期間が3年以内の者も資格を有する。
@@ -3700,23 +3719,23 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>出願資格：
 つぎの１から５のいずれかにも該当する者。
@@ -3729,23 +3748,23 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>出願資格
 ①～⑤のすべてを満たす者
@@ -3759,23 +3778,23 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>【推薦条件】
 ①本学の入学者選抜に合格した場合、入学意思がある者(専願)
@@ -3789,23 +3808,23 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>次の条件を満たすもの
 【1年次入学】
@@ -3837,23 +3856,23 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>【出願資格】以下の全てに該当する者
 (1)日本居住の外国人で、外国において12年の学校教育を修了した者。
@@ -3863,23 +3882,23 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>追手門学院大学（パートナー校制度）</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>【前期】
 ・JLPT N3以上
@@ -3899,23 +3918,23 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>京都外国語大学</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>3名／(１学科につき　1名)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>【各学科共通】
 (1)から(7）のすべてに該当する者
@@ -3948,29 +3967,6 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>園田学園大学</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>5名／5名を超える場合は要相談</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>①授業時間600時間を満たした者かつ、日本語教育の参照枠におけるB2以上の日本語能力を有する者
-②出席率90％以上</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>

--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -139,9 +139,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -956,104 +953,174 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>京都外国語大学</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>外国語学部　日本語学科／国際貢献学部　グローバルスタディーズ学科・グローバル観光学科</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>3名／(１学科につき　1名)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>N１：110点以上での合格</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>A日程：2026/9/24(木)～10/2(金)
+B日程：2026/12/8(火)～12/12(土)</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>A日程：2026/10/23(金)
+B日程：2026/12/19(土)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>A日程：2026/11/1(日)
+B日程：2026/12/25(金)</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>A日程：2026/11/13(金)
+B日程：2027/1/15(金)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>・書類選考　
+・個人面接(15分 オンライン)
+※面接は外国語学部と国際貢献学部グローバル観光学科は【日本語】で、グローバルスタディーズ学科は【英語】で面接を行う。</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>31日</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
           <t>大阪経済法科大学</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>経済学部 経済学科、経営学部 経営学科、法学部 法律学科、国際学部 国際学科</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>前期後期合わせて／計2名／経済学部、経営学部</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>N2以上、またはEJUにおける日本語（読解・聴読解・聴解）が230点以上の者、または、日本語（読解・聴読解・聴解）が200点以上230点未満の者で、下記のいずれ</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>【前期試験】2026年9月24日（木）～10月2日（金）
 【後期試験】2026年12月25日（金）～2027年1月20日（水）</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>【前期試験】2026年10月11日（日）
 【後期試験】2027年2月1日（月）</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>【前期試験】2026年11月2日（月）
 【後期試験】2027年2月12日（金）</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>【前期試験】2026年1月22日（金）
 【後期試験】2027年2月26日（金）</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>志望理由書（600字）
 面接</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>36日</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>大阪観光大学</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>観光学部</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>指定校2名／編入2名</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>N2以上、EJUの日本語得点200点以上、J.TEST600点以上、NAT-TEST2級以上のいずれかを有するもの</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>【指定校推薦】
 A日程：9/7～10/7
@@ -1069,7 +1136,7 @@
 D日程：1/26～2/10</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>【指定校推薦】
 A日程：10/17
@@ -1084,7 +1151,7 @@
 D日程：2/20</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>【指定校推薦】
 A日程：11/2
@@ -1099,7 +1166,7 @@
 D日程：3/2</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>【指定校推薦】
 A日程：11/19
@@ -1114,52 +1181,52 @@
 D日程：3/11</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>書類選考
 個人面談</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>36日</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>園田学園大学</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>経営学部　ビジネス学科</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>5名／5名を超える場合は要相談</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　9月28日（月）～10月7日（水）
 Ⅱ期　11月24日（火）～12月9日（水）
@@ -1167,7 +1234,7 @@
 Ⅳ期　2月15日（月）～3月2日（火）</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　10月18日（日）10：00
 Ⅱ期　12月20日（日）10：00
@@ -1175,7 +1242,7 @@
 Ⅳ期　3月9日（火）10：00</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　10月23日（金）
 Ⅱ期　12月24日（木）
@@ -1183,80 +1250,80 @@
 Ⅳ期　3月12日（金）</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>書類
 面接(10分　100点)
 小論文（10分　100点）</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>43日</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科・経済学部 経済学科・／システム工学部 システム工学科</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>9/14(月)～10/14(水)</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>10/24（土）
 集合時間:12:30
 試験時間:13:00</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>11/1（日）
 10:00～</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>（１次）入学金の納入と手続き書類の提出
 11/2（月）～12/1（火）消印有効
@@ -1264,7 +1331,7 @@
 11/2（月）～12/17（木）</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>エントリーシートに基づく面接
 200点
@@ -1272,46 +1339,46 @@
 しかし、入学試験の結果において、大学の授業に支障があると判断した場合、不合格の可能性あり。</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>44日</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>国際日本・建築&amp;芸術・現代社会・経営／／大手前短期大学／ライフデザイン総合</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>N2以上、NAT-TEST2級以上、J-TEST(A-Cレベル600点以上)、JPT 525点以上のいずれか。</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/10/1(木)～10/15(木)
 B日程：2026/12/14(月)～2027/1/12(火)
@@ -1319,7 +1386,7 @@
 ※消印有効</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>A日程：11/5(木)
 B日程：1/27(水)
@@ -1327,14 +1394,14 @@
 ※試験会場はすべて、西宮夙川キャンパス</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>A日程：11/19(木)
 B日程：2/11(木・祝)
 C日程：3/4(木)</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>入学金納入期日：
 A日程：2025/12/7(月)
@@ -1347,7 +1414,7 @@
 ※詳細は募集要項に記載あり</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>大学
 ①筆記試験 10:00～11:00
@@ -1361,213 +1428,213 @@
 ②個人面接(約15分)</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>45日</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>現代社会学科・放送・メディア映像学科・人間生活学科／（新）デジタルインテリジェンス学科（仮称）</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>各学科／1名／※新学科のみ未定</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>N2以上取得もしくはEJU270点以上</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>前期:9/7(月)～10/16(金)
 後期:2/1(月)～2/15(月)
 ※必着</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>前期:10/24(土)
 後期:2/19(金)</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>前期:11/2(月)
 後期:2/25(木)</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>前期:11/19(木)
 後期:3/4(木)</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>面接（15分）
 ※読み上げ小テスト含む</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>69日</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>情報学部　情報デザイン学科/グローバル学部　グローバル学科/心理学部　心理学科（神戸山手キャンパス）／教育学部　教育福祉学科/経営学部　経営学科（尼崎キャンパス）</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格している者</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>202610月6日（火）～11月9日（月）
 締切日消印有効</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>11月21日（土）</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>12月1日（火）</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>1次手続き入学金20万円　12月17日（木）
 2次手続き授業料等　2027年1月21日（木）</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>個人面接を実施し、出願書類及び指定校推薦書とあわせて総合判定の上、合否を判定します。
 試験は、日本語による個人面接（20分程度）を、尼崎キャンパスにて対面で行います。</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>70日</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>人文学科、管理栄養学科</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>前期　11/1～11/10
 後期　2/3～2/13</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>前期　11/21
 後期　2/22</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>前期　12/1
 後期　3/3</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>前期：入学金納入→12/11
 前期授業料等納入→6/14
@@ -1575,194 +1642,194 @@
 前期授業料等納入→6/15</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>面接
 （推薦書・志望理由書）を参考にする</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>70日</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>N2以上またはEJU「日本語（記述問題を含む）」230点以上の者(聴読解及び読解で各100点以上、記述30点以上)。</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>2026年11月1日（日）～11月10日（火）
 締切日必着（郵送に限ります。速達　簡易書留で送付します）</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>2026年11月21日（土）
 口頭試問:13:00～</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>2026年12月7日（月）
 13：00～</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>入学金・春学期分学費・諸会費の納付期間2026年12月7日（月）～2027年1月29日（金）</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>日本語による口頭試問　配点100点</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>71日</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>国際学部　日本学科（留学生対象）</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>N2程度の日本語能力を有する者</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>2026/11/2(月)～11/11(水)
 ※必着</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>面接：
 2026/11/20(金)
 ※学校長からの推薦書・調査書及び課題論文をもとに「書類審査」・「面接」により選抜します。</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>2026/12/1(火)
 ※「選考結果通知書」は学校宛てに郵送します。
 本人へは、出願時に登録していただくPost@net のマイページから発表します。</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>【第1次】2026/12/15(水)…入学金
 【第2次】2026/1/20(火)…春学期分納付金と入学手続書類＜必着＞</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>推薦書・調査書及び課題論文をもとに
 「書類審査」・「面接」により選抜</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>72日</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>1期：11月2日(月)～11月12日(木)
 Ⅱ期：12月1日(火)～12月16日(水)
@@ -1771,7 +1838,7 @@
 Ⅴ期：2月24日(水)～3月11日(木)</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月14日(土)
 Ⅱ期：12月19日(土)
@@ -1780,7 +1847,7 @@
 Ⅴ期：3月13日(土)</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月18日(水)
 Ⅱ期：12月23日(水)
@@ -1789,7 +1856,7 @@
 Ⅴ期：3月18日(木)</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月26日(木)
 Ⅱ期：1月7日(木)
@@ -1798,56 +1865,56 @@
 Ⅴ期：3月26日(金)</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>・書類審査
 ・個人面接(日本語の口頭試問含むオンライン試験)</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>87日</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者、または、EJU(日本語/記述除く)200点以上の者。</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>85%以上</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年11月9日(月)～11月27日(金)
 (WEB出願は24日の午後5時まで)
@@ -1858,21 +1925,21 @@
 いずれも必着締め切り</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月5日(土)
 Ⅱ期：2027年2月7日(日)
 Ⅲ期：2027年2月26日(金)</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月11日(金)
 Ⅱ期：2027年2月12日(金)
 Ⅲ期：2027年3月5日(金)</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2027年1月13日(水)
 Ⅱ期：2027年2月26日(金)
@@ -1880,56 +1947,56 @@
 必着締め切り</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>①出願書類審査(志望理由書、在籍校での成績及び出席率、推薦書を含む)
 ②面接試験(15分)…集団面接</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>90日</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>経済経営学科、国際文化ビジネス・観光学科</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>N2相当であるもの（※N2相当は下記いずれかの基準）</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 【前期】
@@ -1942,21 +2009,21 @@
 窓口の場合は16:00まで</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/13
 後期：2/22</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/24
 後期：3/4</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期
@@ -1967,74 +2034,74 @@
 （第二次）〃</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>書類審査
 本学独自の日本語能力試験
 面接</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>100日</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>国際教養学部 英語・国際文化学科、／社会学部 社会学科/社会福祉学科(※現：ソーシャルデザイン学科で2027年4月に社会福祉学科に名称変更構想中)、／法学部 法律学科、経済学部 経済学科、経営学部 経営学科、工学部 工学科</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>N2レベル以上の者、またはEJUの日本語科目(読解、聴解及び聴読解)の得点が220点以上の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>2026年12月1日(火)～12月10日(木)
 ※入学検定料は締め切り12/11(金)13時振込完了
 締切日当日消印有効</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026/12/19（土）</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>2026/12/24（木）</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>2026年12月24日(木)～
 2027年2月12日(金)
@@ -2042,7 +2109,7 @@
 入学申込金、春学期授業料一括納入</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>・面接
 ・小論文
@@ -2050,198 +2117,50 @@
 (EJUの成績確認書またはN２以上の成績証明書)/工学部工学科のみEJUの数学コース2及び理科の成績確認書も</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>15日</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>追手門学院大学（パートナー校制度）</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>国際学部 国際学科 グローバルスタディーズ専攻</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>日本語要件の記載なし</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>記載なし</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年9月10日（木）～2026年9月16日（水）
-【後期】2026年12月18日（金）～2027年1月12日（火）
-※当日消印有効</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>前期：2026年10月3日（土）
-後期：2027年1月28日（木）</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年10月9日（金）
-【後期】2027年2月18日（木）</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年11月9日（月）
-【後期】2027年2月26日（金）</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>筆記試験（日本語読解・小論文）
-面接（日本語・英語）</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>日语（N3以上）你够，但还另外要求英语成绩（TOEFL iBT74 / IELTS5.5 / TOEIC800 / Duolingo100）</t>
-        </is>
-      </c>
+      <c r="N20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>31日</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>京都外国語大学</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>外国語学部　日本語学科／国際貢献学部　グローバルスタディーズ学科・グローバル観光学科</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>3名／(１学科につき　1名)</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>N１：110点以上での合格</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>記載なし</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>A日程：2026/9/24(木)～10/2(金)
-B日程：2026/12/8(火)～12/12(土)</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>A日程：2026/10/23(金)
-B日程：2026/12/19(土)</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>A日程：2026/11/1(日)
-B日程：2026/12/25(金)</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>A日程：2026/11/13(金)
-B日程：2027/1/15(金)</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>・書類選考　
-・個人面接(15分 オンライン)
-※面接は外国語学部と国際貢献学部グローバル観光学科は【日本語】で、グローバルスタディーズ学科は【英語】で面接を行う。</t>
-        </is>
-      </c>
-      <c r="N21" s="9" t="inlineStr">
-        <is>
-          <t>日本語学科要 N1 110 分以上，报不了。グローバルスタディーズ／グローバル観光学科用 N2 100 分以上可以报</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>名古屋経済大学</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>経済学部現代経済学科、経営学部経営学科、法学部ビジネス法学科</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>N2（B2）レベル相当以上の日本語能力があると認められる者</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　2025年9月30日（水）10:00～10月9日（金）15:00
 Ⅱ期　2025年10月28日（水）10:00～11月4日（水）15:00
@@ -2253,7 +2172,7 @@
 ※出願書類提出は締め切り日当日消印有効</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　10月17日（土）
 Ⅱ期　11月15日（日）
@@ -2263,7 +2182,7 @@
 Ⅵ　3月5日（金）</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　11月2日（月）
 Ⅱ期　12月1日（火）
@@ -2273,7 +2192,7 @@
 Ⅵ期　3月11日（木）</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　11月19日（木）
 Ⅱ期　12月17日（木）
@@ -2283,7 +2202,7 @@
 Ⅵ期　3月23日（火）</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>書類審査、面接、小論文により、合否を決定します。
 小論文は以下の2題を出題します。解答時間は60分です。
@@ -2292,9 +2211,79 @@
 ②試験当日にテーマ公表、読解作文（200字程度）</t>
         </is>
       </c>
+      <c r="N21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>15日</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>追手門学院大学（パートナー校制度）</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>国際学部 国際学科 グローバルスタディーズ専攻</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>2名</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>日本語要件の記載なし</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年9月10日（木）～2026年9月16日（水）
+【後期】2026年12月18日（金）～2027年1月12日（火）
+※当日消印有効</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>前期：2026年10月3日（土）
+後期：2027年1月28日（木）</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年10月9日（金）
+【後期】2027年2月18日（木）</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年11月9日（月）
+【後期】2027年2月26日（金）</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>筆記試験（日本語読解・小論文）
+面接（日本語・英語）</t>
+        </is>
+      </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>条件上 N2 可以。但报名期间栏还是 2025 年的日期，可能是漏更新了</t>
+          <t>募集要項原文は日语组と英语组それぞれに「いずれかを有する者」＝AND。日语 N3 你够，但**必须另有英语成绩**（TOEIC800／IELTS5.5／TOEFL iBT74／Duolingo100 之一）。反面：英語能力に応じて最大100%の授業料免除あり</t>
         </is>
       </c>
     </row>
@@ -2338,48 +2327,48 @@
       <c r="M23" s="9" t="inlineStr"/>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>名单上标着「編集中」，条件和日程都还没写</t>
+          <t>指定校名单上条件栏是空的、日程也未记载（名单标「編集中」）。学费は官网で確認済（138.7万）だが、出願条件そのものが不明なので判定できない ← 学校の進路担当に確認が必要</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>太成学院大学</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>健康スポーツ学科、看護学科／心理カウンセリング学科、現代ビジネス学科</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr"/>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>N2（112点以上）またはN1</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>A日程：8/24-9/3
 B日程：9/14-10/1
@@ -2387,7 +2376,7 @@
 D日程：1/4-1/28</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>A日程：9/13
 B日程：10/10
@@ -2395,7 +2384,7 @@
 D日程：2/5</t>
         </is>
       </c>
-      <c r="K24" s="14" t="inlineStr">
+      <c r="K24" s="13" t="inlineStr">
         <is>
           <t>A日程：9/18
 B日程：10/16
@@ -2403,7 +2392,7 @@
 D日程：2/12</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="L24" s="13" t="inlineStr">
         <is>
           <t>A日程:
 入学金10/2
@@ -2423,75 +2412,75 @@
 2回目3/16</t>
         </is>
       </c>
-      <c r="M24" s="14" t="inlineStr">
+      <c r="M24" s="13" t="inlineStr">
         <is>
           <t>面接
 書類</t>
         </is>
       </c>
-      <c r="N24" s="14" t="inlineStr">
+      <c r="N24" s="13" t="inlineStr">
         <is>
           <t>要求 N2 112 分以上，你 111 分差 1 分（EJU220／JPT525／J.TEST C级600 也可以替代）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>30日</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>日本工業大学</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr"/>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr"/>
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>第１期：2026年9月1日（火）～10月1日（木）必着
 第2期：2026年12月10日(木)～2027年1月19日(火)必着</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>第１期：2026年10月11日（日）
 第２期：2027年1月29日(金)
 場所：日本工業大学埼玉キャンパス</t>
         </is>
       </c>
-      <c r="K25" s="14" t="inlineStr">
+      <c r="K25" s="13" t="inlineStr">
         <is>
           <t>第１期：2026年11月2日（月）
 第2期：2027年2月8日(月)</t>
         </is>
       </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="L25" s="13" t="inlineStr">
         <is>
           <t>入学金納入
 第1期：2026年11月17日（火）
@@ -2501,136 +2490,136 @@
 第2期：2027年3月9日(火)</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr">
+      <c r="M25" s="13" t="inlineStr">
         <is>
           <t>・書類審査（出席・成績証明書、志望理由書、日本留学試験の受験票）
 ・個人面接(15分)。</t>
         </is>
       </c>
-      <c r="N25" s="14" t="inlineStr">
+      <c r="N25" s="13" t="inlineStr">
         <is>
           <t>必须有 EJU（日语230分，还要考数学课程2）。不认 JLPT</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>31日</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>平安女学院大学</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>国際観光学部　国際観光学科</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>N2以上に合格した方。</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>1期：2026年9/21(月)～10/2(金)
 2期：2027年1/25(月)～2/8(月)</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>1期：2026年10/11(日)13:30～
 2期：2027年2/14(日)13:30～</t>
         </is>
       </c>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>1期：2026年10/16(金)
 2期：2027年2/19(金)</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="L26" s="13" t="inlineStr">
         <is>
           <t>1期：2026年12/4(金)
 2期：2027年3/12(金)</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr">
+      <c r="M26" s="13" t="inlineStr">
         <is>
           <t>面接</t>
         </is>
       </c>
-      <c r="N26" s="14" t="inlineStr">
+      <c r="N26" s="13" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>42日</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>駒沢女子大学・短期大学</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>国際日本語学科・人間関係学科・心理学科・観光文化学科・空間デザイン学科</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>N2相当の者</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>※入学検定料振込：10:00～15:00
 ※必要書類郵送：最終日消印有効
@@ -2642,7 +2631,7 @@
 Ⅲ₋b期：2/18(木)～2/25(木)</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>Ⅰ₋a期：10/24(土)
 Ⅰ₋b期：11/21(土)
@@ -2652,7 +2641,7 @@
 Ⅲ₋b期：3/10(水)</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>Ⅰ₋a期：11/2(月)
 Ⅰ₋b期：12/1(火)
@@ -2662,158 +2651,158 @@
 Ⅲ₋b期：3/12(金)</t>
         </is>
       </c>
-      <c r="L27" s="14" t="inlineStr">
+      <c r="L27" s="13" t="inlineStr">
         <is>
           <t>‐</t>
         </is>
       </c>
-      <c r="M27" s="14" t="inlineStr">
+      <c r="M27" s="13" t="inlineStr">
         <is>
           <t>面接（15分程度）
 書類審査</t>
         </is>
       </c>
-      <c r="N27" s="14" t="inlineStr">
+      <c r="N27" s="13" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>44日</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>大阪国際大学</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>経営経済学部 経営学科/経済学科、／国際教養学部 国際コミュニケーション学科/国際観光学科</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>各1名ずつ</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr">
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>2026年10月5日～10月15日
 （消印有効）</t>
         </is>
       </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>2026-10-24 00:00:00</t>
         </is>
       </c>
-      <c r="K28" s="14" t="inlineStr">
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>2026-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="L28" s="14" t="inlineStr">
+      <c r="L28" s="13" t="inlineStr">
         <is>
           <t>入学金〆切：11月6日～11月20日
 前期学費納入〆切：11月6日～12月18日</t>
         </is>
       </c>
-      <c r="M28" s="14" t="inlineStr">
+      <c r="M28" s="13" t="inlineStr">
         <is>
           <t>書類選考
 面接</t>
         </is>
       </c>
-      <c r="N28" s="14" t="inlineStr">
+      <c r="N28" s="13" t="inlineStr">
         <is>
           <t>必须有 EJU（日语200分）。不认 JLPT</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>135日</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>近畿大学</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>国際学部国際学科グローバル専攻</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>前期・後期合計／2名</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>【前期】2026年8月24日（月）～8月27日（木）
 【後期】2027年1月8日（金）～1月14日（木）</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>【前期試験】2026年10月10日（土）
 【後期試験】2027年2月20日（土）</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>【前期試験】2026年11月9日（月）
 【後期試験】2027年3月9日（火）</t>
         </is>
       </c>
-      <c r="L29" s="14" t="inlineStr">
+      <c r="L29" s="13" t="inlineStr">
         <is>
           <t>【前期試験】
 第一次手続：2026年11月9日（月）～11月27日（金）
@@ -2821,207 +2810,207 @@
 【後期試験】2027年3月9日（火）～3月15日（月）</t>
         </is>
       </c>
-      <c r="M29" s="14" t="inlineStr">
+      <c r="M29" s="13" t="inlineStr">
         <is>
           <t>口頭試問、日本留学試験成績
 総合して合否を判定</t>
         </is>
       </c>
-      <c r="N29" s="14" t="inlineStr">
+      <c r="N29" s="13" t="inlineStr">
         <is>
           <t>必须有 EJU（日语300分＋综合科目100分＋总分400分）。不认 JLPT</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>135日</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>神戸学院大学</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>グローバル・コミュニケーション学部　グローバル・コミュニケーション学科日本語コース</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I30" s="14" t="inlineStr">
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>2027年1月6日（水）～1月14日（木）必着</t>
         </is>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>2月10日（水）</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>2月19日（金）</t>
         </is>
       </c>
-      <c r="L30" s="14" t="inlineStr">
+      <c r="L30" s="13" t="inlineStr">
         <is>
           <t>第1次:2月22日（月）～3月1日（月）厳守
 第2次:2月22日（月）～3月8日（月）厳守</t>
         </is>
       </c>
-      <c r="M30" s="14" t="inlineStr">
+      <c r="M30" s="13" t="inlineStr">
         <is>
           <t>・書類選考
 ・面接
 13:10～</t>
         </is>
       </c>
-      <c r="N30" s="14" t="inlineStr">
+      <c r="N30" s="13" t="inlineStr">
         <is>
           <t>必须有 EJU（日语240分）。不认 JLPT</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>上海大学</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>中国語学部中国語学科</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>2026年5月1日～出願終了まで</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="L31" s="13" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="M31" s="14" t="inlineStr">
+      <c r="M31" s="13" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="N31" s="14" t="inlineStr">
+      <c r="N31" s="13" t="inlineStr">
         <is>
           <t>要求中国籍以外，你不符合</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>中日本自動車短期大学（岐阜）</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>自動車工学科(2年)・モータースポーツエンジニアリング学科(3年)</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>N2程度の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="13" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I32" s="14" t="inlineStr">
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>10月期　9月10日-17日
 11月期　10月15日-22日
@@ -3029,7 +3018,7 @@
 2月期　1月15日-22日</t>
         </is>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>10月期　10月11日
 11月期　11月15日
@@ -3037,7 +3026,7 @@
 2月期　2月7日</t>
         </is>
       </c>
-      <c r="K32" s="14" t="inlineStr">
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>10月期　10月19日
 11月期　11月23日
@@ -3045,7 +3034,7 @@
 2月期　2月15日</t>
         </is>
       </c>
-      <c r="L32" s="14" t="inlineStr">
+      <c r="L32" s="13" t="inlineStr">
         <is>
           <t>1次
 10月期　11月13日
@@ -3055,59 +3044,59 @@
 (2次は全て3月15日）</t>
         </is>
       </c>
-      <c r="M32" s="14" t="inlineStr">
+      <c r="M32" s="13" t="inlineStr">
         <is>
           <t>面接・書類審査</t>
         </is>
       </c>
-      <c r="N32" s="14" t="inlineStr">
+      <c r="N32" s="13" t="inlineStr">
         <is>
           <t>短期大学（你指定排除）</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>大阪女学院大学</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>大阪女学院大学（3年次編入学）／大阪女学院短期大学／／国際教養学部　国際教養学科</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>共通
 一期：9/24(木)∼9/30(水)
@@ -3118,7 +3107,7 @@
 六期：2027/3/3(水)∼3/9(火)</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>共通
 一期：10/11(日)
@@ -3129,7 +3118,7 @@
 六期：2026/3/17(水)</t>
         </is>
       </c>
-      <c r="K33" s="14" t="inlineStr">
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>共通
 一期：10/16(金)
@@ -3140,7 +3129,7 @@
 六期：2027/3/17(水)</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="L33" s="13" t="inlineStr">
         <is>
           <t>入学金(100,000円納入　書類提出期日)
 一期：11/2(月)
@@ -3158,61 +3147,61 @@
 六期：2025/3/27(火)</t>
         </is>
       </c>
-      <c r="M33" s="14" t="inlineStr">
+      <c r="M33" s="13" t="inlineStr">
         <is>
           <t>共通
 面接(日本語)約20分
 ※うち3分程度で「日本語と英語をどのように勉強してきたのか、また入学後どのように勉強したいのか」を日本語で発表</t>
         </is>
       </c>
-      <c r="N33" s="14" t="inlineStr">
+      <c r="N33" s="13" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>大阪キリスト教短期大学</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>①介護福祉別科／②教育テックコースDXグローバルクラス</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>介護福祉別科：2名／教育テック：3名</t>
         </is>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>N2 相当またはCEFR B2 以上の日本語力の習得を目指す意志のある者</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="I34" s="13" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年8月7日(金)～8月21日(金)
@@ -3220,7 +3209,7 @@
 2026年8月3日(月)～2026年8月17日(月)</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年8月29日(土)
@@ -3228,7 +3217,7 @@
 8月29日（土）</t>
         </is>
       </c>
-      <c r="K34" s="14" t="inlineStr">
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年9月11日(金)
@@ -3236,12 +3225,12 @@
 9月14日（月）</t>
         </is>
       </c>
-      <c r="L34" s="14" t="inlineStr">
+      <c r="L34" s="13" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="M34" s="14" t="inlineStr">
+      <c r="M34" s="13" t="inlineStr">
         <is>
           <t>【介護福祉学科】
 書類審査
@@ -3256,7 +3245,7 @@
 日本語での面接を実施</t>
         </is>
       </c>
-      <c r="N34" s="14" t="inlineStr">
+      <c r="N34" s="13" t="inlineStr">
         <is>
           <t>短期大学（你指定排除）</t>
         </is>
@@ -3284,44 +3273,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>学校名</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>枠</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>推薦条件（原文）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>ものつくり大学</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>①外国において学校教育における12年教育の課程を修了したもので、外国の大学入学資格を有するもの
 ②外国において、12年の課程修了相当の学力認定試験に合格したもの
@@ -3337,22 +3326,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>芦屋大学</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>5名</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>推薦条件
 ①大学生活に支障のない経済状況にある者
@@ -3366,22 +3355,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>神戸医療未来大学</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>【姫路キャンパス】／２名／／【大阪天王寺キャンパス】／1名</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>【出願資格】(1～3のいずれかに該当する者)
 (１)外国籍を有し、2027年4月までに18歳に達する者で、本学での授業に支障のない程度(日本語教育の参照枠でB２相当以上)の日本語能力を有すると認められる者。
@@ -3397,22 +3386,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>流通科学大学</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>3名</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>出願資格　
 2027年度外国人留学生入試の出願資格に該当し、本学が指定する日本語学校等を2027年3月に卒業見込みの者で、本学を専願とする者。
@@ -3426,515 +3415,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>大阪経済法科大学</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>前期後期合わせて／計2名／経済学部、経営学部</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>①専願する者
-②JLPTN2以上、またはEJUにおける日本語（読解・聴読解・聴解）が230点以上の者、または、日本語（読解・聴読解・聴解）が200点以上230点未満の者で、下記のいずれかのスコアを取得している者。
-・EJUにおける総合科目（社会）、数学コース1、コース2のいずれかが50%（100点）以上の者。
-・英語外部検定試験においてTOEFL iBT40以上、IELTS3.5以上、TOEIC(L&amp;R+S&amp;W)650点以上のいすれかを取得している者。
-③日本語学校等における出席率が原則として90%以上の者。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>大阪観光大学</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>指定校2名／編入2名</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>①2027年3月卒業見込みで、学校長が推薦したもの。
-②出席率が90％以上のもの。
-③JLPTN2以上、EJUの日本語得点200点以上、J.TEST600点以上、NAT-TEST2級以上のいずれかを有するもの
-④外国において12年以上の課程を修了したもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>園田学園大学</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>5名／5名を超える場合は要相談</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>①授業時間600時間を満たした者かつ、日本語教育の参照枠におけるB2以上の日本語能力を有する者
-②出席率90％以上</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>大阪産業大学</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>①日本国籍を有しない者
-②下記（1）～（3）のいずれかを満たす者
-　（1）外国において、学校教育における12年の課程を修了した者または2027年3月まで修了見込みの者
-　（2）外国において、12年の課程修了相当の学力認定試験に合格した者で2027年3月31日までに18歳に達する者
-　（3）本学が上記（1)、（2）と同等以上の学力があると認めた者
-③12年間の課程のうち日本の小学校、中学校、高等学校及び中等教育学校に在学した期間が通算3年以内である者も含むものとする。
-④本学が指定する日本語学校に在籍し出席率が90％以上で、（1）～（3）いずれかの推薦基準を満たし、学校長の推薦を受けたもの。
-　（1）「JLPT2」以上に合格したもの
-　（2）「J．TEST　C級」以上合格したもの
-　（3）「独立行政法人日本学生支援機構」の実施する2026年度のEJUにおいて、「日本語(読解/聴解・聴読解)」科目の点数が240点以上の者
-⑤本学専願者に限る</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>大手前大学</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>【大学・短大共通条件↓】
-出席率90%以上
-日本国籍を有しない者で、次の①②③のいずれかに加え、④に該当する者
-①外国において学校教育における12年の課程を修了した者、またはこれに準ずる文部科学大臣が指定した課程を修了した者。
-ただし、中等教育の課程修了までに12年を要しない国については文部科学大臣が指定している日本の大学に入学するための準備教育を行う課程(準備教育課程)または研修施設の課程などを修了した者。
-なお、12年の課程のうち、日本の高等学校もしくは中等教育学校(後期課程)での在籍期間が3年以内の者も資格を有する。
-②本学において個別の入学資格審査により上記と同等以上の資格があると認められた者。
-③国際バカロレア資格またはドイツ連邦共和国におけるアビトゥア資格など、外国における大学入学資格を授与された者。
-④次のいずれかに該当する者
-【A・B日程に出願する者】入学後の在留資格が原則として「留学」である者
-【C日程に出願する者】出願時に「留学」の在留資格を有する者
-【大学】
-出願資格：
-2024年4月1日以降に実施されたEJU220点以上(読解・聴解・聴読解)、JLPT　N2以上、NAT-TEST2級以上、J-TEST(A-Cレベル600点以上)、JPT 525点以上のいずれか。
-※その他要項は、募集要項に記載のとおり。
-【短期大学】
-※大手前大学に編入希望者であることが前提
-出願資格：
-2024年4月1日以降に実施された以下の試験の通知書の写しを提出した者↓
-N3以上、NAT-TEST3級、J.TEST:D-Eレベル500点以上、JPT430点以上525点未満、PJCレベルD⁺、PJC bridgeレベルA⁺
-↑※これらより上位の資格・点数の者は出願不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>羽衣国際大学</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>各学科／1名／※新学科のみ未定</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>出願資格：次の各項のすべてに該当する者
-①貴校の校長が推薦し、かつ本学を専願とする者
-②外国籍を有し、出入国管理及び難民認定法による「留学」の在留資格を2027年3月31日までに取得可能なもの
-③次のいずれかに該当する者
-1.外国において12年の課程を終了、または2027年3月31日までに修了見込みの者
-2. 1.に準ずるも者で文部科学大臣の指定した者
-3.本学が実施する個別の入学資格審査により、高等学校を卒業した者と同等以上の学力があると認められた18歳以上の者
-推薦基準：
-次の各項のすべてに該当する者
-①貴校における入学時からの出席率が90％以上の者
-②大学入学時に日本語による受講が可能な日本語能力を有する者（下記いずれか）
-【放送メディア映像学】
-・N2以上取得もしくはEJU270点以上
-【現代社会学科＆人間生活学科】
-・N2以上取得もしくはEJU240点以上
-③大学生活を送る上で十分な支弁能力を兼ね備えていると認められる者
-④志望学科の学問分野に深く関心のある者</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>関西国際大学</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>全学部合計4名</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>出願資格
-外国籍を有する者で、（1）出願資格のいずれかに該当し、かつ（2）出願条件と（3）（4）を満たし、本学を専願とする者に出願資格があります。
-（1）出願資格
-次のいすれかに該当する者
-①外国において、学校教育における12年の課程を修了した者または2027年3月31日までに修了見込みの者。ただし、12年課程のうち日本の小学校・中学校・高校に在籍した場合はその期間が通算3年以内に限る。
-②その他、本学が上記と同等以上の学力があると認めた者で、2027年3月31日までに18歳に達する者
-（2）出願条件
-①～⑤のいすれかに該当し、在籍する日本語学校・専門学校の出席率が原則として95％以上の者
-①JLPT　N2以上に合格している者
-②EJU読解、聴解、聴読解の合計が220点以上の者
-③J．TEST　A‐CレベルのC級以上を取得したもの
-④NAT‐TESTの2級以上を取得したもの
-⑤JPT日本語能力試験525点以上を取得した者
-（3）学校長の推薦を受けた者
-（4）在留資格「留学」を取得でき、2027年4月1日に本学に入学可能なもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>相愛大学</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>各学科／前期：5名／後期：若干名</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>【人文学科】
-１～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
-１）外国籍を有し、外国において日本の高等学校卒業に相当する12年の学校教育を修了した者、またはこれに準じる者
-２）日本語学校を2027年度中に卒業した者、または卒業見込みの者で成績優秀でかつ学校長が推薦する者
-３）2027年4月1日現在において満18歳に達した者で、原則として日本居住が3年以内の者
-４）次のa～cいずれかに該当する者
-a)JLPTを受験し、N2以上に合格した者
-b)EJU　EJU240点以上（記述を含む）
-c)本学が実施する「出願資格認定試験」で認定を受けた者
-５）出席率95％以上の者
-６）本学の教育方針を理解し、志望学科に対する明確な志向とそれに相応しい能力・適正を備えた者
-【管理栄養学科】
-１～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
-１）外国籍を有し、外国において日本の高等学校卒業に相当する12年の学校教育を修了した者、またはこれに準じる者
-２）日本語学校を2027年度中に卒業した者、または卒業見込みの者で成績優秀でかつ学校長が推薦する者
-３）2027年4月1日現在において満18歳に達した者で、原則として日本居住が3年以内の者
-４）次のa～cいずれかに該当する者
-a)JLPTを受験し、N2以上に合格した者
-b)EJU　EJU200点以上（記述を含む）
-c)本学が実施する「出願資格認定試験」で認定を受けた者
-５）出席率90％以上の者
-６）本学の教育方針を理解し、志望学科に対する明確な志向とそれに相応しい能力・適正を備えた者</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>大阪経済大学　国際共創部　国際共創学科</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>1名</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>①外国の国籍を有し、外国において学校教育における12年の課程を修了した者、もしくは2027年3月までに修了見込みの者
-※12年の課程のうち、日本の高等学校での在籍期間が3年以内の者も資格を有する。
-②文部科学省令により上記①と同等以上の資格を有する者、もしくは上記①と同等以上の資格を有すると本学が認めた者。
-③本学受験時までに来日して6か月以上経過している者で2027年3月31日までに日本語学校を卒業（修了）見込みの者。
-④「出入国管理及び難民認定法」による「留学」の在留資格を取得または更新できる者。
-⑤JLPT　N2以上またはEJU「日本語（記述問題を含む）」230点以上の者(聴読解及び読解で各100点以上、記述30点以上)。
-⑥本学が推薦を依頼する日本語学校に在学し、その日本語学校学校長が責任をもって推薦する者。
-⑦本学国際共創学部を第1志望とし、強く入学を希望する者（合格すれば、必ず入学する者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>天理大学</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>出願資格：
-つぎの１から５のいずれかにも該当する者。
-1．本大学の建学の精神を理解しその趣旨にそう者
-2．本大学の指定する学校を2027年3月修了見込みの者で、出身学校長が推薦し、かつ本大学を専願する者
-3．外国籍を有し、外国において学校教育における12年の課程を修了した者、もしくはこれに準ずる者として文部科学大臣の指定した者
-4．学業を目的として日本に居住し、「出入国管理及び難民認定法」による「留学」の在留資格を有する者またはそれに切り替え可能な在留資格を有する者
-5．本大学の指定する学校在学中の出席率が90％以上の学生で、日本留学試験（日本語）200点以上または日本語能力試験N2程度の日本語能力を有する者
-※出願後の志望専攻の変更は一切認められない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>育英館大学</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>1名</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>出願資格
-①～⑤のすべてを満たす者
-①2027年3月に本学が指定した日本語学校を卒業見込みの者。
-②出席状況が95%以上である者。
-③日本語能力が以下のいずれかである者
-　　・EJUの日本語(読解・聴解・聴読解)の合計点が200点以上
-　　・JLPT N2以上
-④合格した場合に必ず入学する意思のある者。
-⑤学校長の推薦を受けた者。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>山梨学院大学</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>【推薦条件】
-①本学の入学者選抜に合格した場合、入学意思がある者(専願)
-②誠実で協調性があり勉学意欲が旺盛で、経営学部経営学科の修業に適性のある者。
-③日本語能力試験N2以上に合格した者、または、EJU(日本語/記述除く)200点以上の者。
-④出席率(時間数換算)が85%以上の者。
-⑤本学における4年間の学費・生活費などの支弁が可能である者。
-⑥日本の法律を遵守し、健全な留学生活を送ることが約束できるもの。
-※指定校で受験の場合、入学選抜の筆記試験(日本語総合試験)免除。
-ただし、JLPT N2合格者でCEFR判定がB1の場合、またはEJUの受験年度・回の平均点未満の場合は、推薦書の中に日本語学習の到達度に「CEFR B2 相当の学習をしている」(または卒業時までにB2に達する)旨を記述すること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>神戸国際大学</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>（1年入学）各学科1名／（2年編入）1名</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>次の条件を満たすもの
-【1年次入学】
-①外国で高等学校に相当する学校の過程を修了した者
-②日本で日本語学校または、専門学校を2026年3月までに修了見込みの者
-③学校長が推薦するもの
-④本学を専願するもの
-⑤在留資格が出入国管理法の「留学」のもの
-⑥日本語能力がN2相当であるもの（※N2相当は下記いずれかの基準）
-・日本語能力試験（JLPT）N2受験予定のもの
-・日本留学試験日本語（EJU）（記述除く）200点以上のもの
-・実用日本語検定（J₋TEST）A～Cレベル試験600点以上のもの
-・JPT日本語能力試験525点以上のもの
-⑦在籍期間中の出席率が90％以上であるもの
-【編入】
-①日本で日本語学校または、専門学校を2026年3月までに修了見込みの者
-②以下の①～③いずれかに該当するもの
-・日本国内の大学、短期大学または高等学校専門学校を卒業した者
-・日本国内の専修学校専門課程（修業年限が2年以上であること、その他文部科学大臣が定める基準を満たす者に限る）を修了した者
-・日本国外の大学で2年以上の課程を修了した者
-③学校長が推薦するもの
-④本学を専願するもの
-⑤在留資格が出入国管理法の「留学」のもの
-・日本語能力がN2以上を取得しているもの
-・日本留学試験日本語（EJU）450点満点のうち225点以上を取得している
-・実用日本語検定（J₋TEST）A～Cレベル試験600点以上のもの
-・JPT日本語能力試験525点以上のもの
-⑦在籍期間中の出席率が90％以上であるもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>桃山学院大学</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>6名</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>【出願資格】以下の全てに該当する者
-(1)日本居住の外国人で、外国において12年の学校教育を修了した者。
-(2)日本語能力試験N2レベル以上の者、またはEJUの日本語科目(読解、聴解及び聴読解)の得点が220点以上の日本語能力を有する者。
-なお工学部工学科を志願する者は、これに加えて、EJUの「数学コース2」の得点が100点以上で、かつ「理科」の得点を有する者。
-(3)専願</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>追手門学院大学（パートナー校制度）</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>【前期】
-・JLPT N3以上
-・EJU180点以上（2025年第二回、2026年第一回）
-・J.TEST A-Cレベル500点以上
-・ビジネス日本語能力テスト420点以上
-・JPT500点以上　いずれかを有する者
-・TOEFL iBT 74以上、IELTS 5.5以上、TOEIC 800以上、Duolingo English Test100以上のいずれかを有する者
-【後期】
-・JLPT N3以上
-・EJU180点以上（2025年第二回、2026年第一回、2026年第二回）
-・J.TEST A-Cレベル500点以上
-・ビジネス日本語能力テスト420点以上
-・JPT500の点以上　いずれかを有する者
-・TOEFL iBT 74以上、IELTS 5.5以上、TOEIC 800以上、Duolingo English Test100以上のいずれかを有する者
-英語能力に応じて最大100%の授業料免除制度あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>京都外国語大学</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>3名／(１学科につき　1名)</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>【各学科共通】
 (1)から(7）のすべてに該当する者
@@ -3967,23 +3463,480 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>大阪経済法科大学</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>前期後期合わせて／計2名／経済学部、経営学部</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>①専願する者
+②JLPTN2以上、またはEJUにおける日本語（読解・聴読解・聴解）が230点以上の者、または、日本語（読解・聴読解・聴解）が200点以上230点未満の者で、下記のいずれかのスコアを取得している者。
+・EJUにおける総合科目（社会）、数学コース1、コース2のいずれかが50%（100点）以上の者。
+・英語外部検定試験においてTOEFL iBT40以上、IELTS3.5以上、TOEIC(L&amp;R+S&amp;W)650点以上のいすれかを取得している者。
+③日本語学校等における出席率が原則として90%以上の者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>大阪観光大学</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>指定校2名／編入2名</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>①2027年3月卒業見込みで、学校長が推薦したもの。
+②出席率が90％以上のもの。
+③JLPTN2以上、EJUの日本語得点200点以上、J.TEST600点以上、NAT-TEST2級以上のいずれかを有するもの
+④外国において12年以上の課程を修了したもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>園田学園大学</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>5名／5名を超える場合は要相談</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>①授業時間600時間を満たした者かつ、日本語教育の参照枠におけるB2以上の日本語能力を有する者
+②出席率90％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>大阪産業大学</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>①日本国籍を有しない者
+②下記（1）～（3）のいずれかを満たす者
+　（1）外国において、学校教育における12年の課程を修了した者または2027年3月まで修了見込みの者
+　（2）外国において、12年の課程修了相当の学力認定試験に合格した者で2027年3月31日までに18歳に達する者
+　（3）本学が上記（1)、（2）と同等以上の学力があると認めた者
+③12年間の課程のうち日本の小学校、中学校、高等学校及び中等教育学校に在学した期間が通算3年以内である者も含むものとする。
+④本学が指定する日本語学校に在籍し出席率が90％以上で、（1）～（3）いずれかの推薦基準を満たし、学校長の推薦を受けたもの。
+　（1）「JLPT2」以上に合格したもの
+　（2）「J．TEST　C級」以上合格したもの
+　（3）「独立行政法人日本学生支援機構」の実施する2026年度のEJUにおいて、「日本語(読解/聴解・聴読解)」科目の点数が240点以上の者
+⑤本学専願者に限る</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>大手前大学</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>【大学・短大共通条件↓】
+出席率90%以上
+日本国籍を有しない者で、次の①②③のいずれかに加え、④に該当する者
+①外国において学校教育における12年の課程を修了した者、またはこれに準ずる文部科学大臣が指定した課程を修了した者。
+ただし、中等教育の課程修了までに12年を要しない国については文部科学大臣が指定している日本の大学に入学するための準備教育を行う課程(準備教育課程)または研修施設の課程などを修了した者。
+なお、12年の課程のうち、日本の高等学校もしくは中等教育学校(後期課程)での在籍期間が3年以内の者も資格を有する。
+②本学において個別の入学資格審査により上記と同等以上の資格があると認められた者。
+③国際バカロレア資格またはドイツ連邦共和国におけるアビトゥア資格など、外国における大学入学資格を授与された者。
+④次のいずれかに該当する者
+【A・B日程に出願する者】入学後の在留資格が原則として「留学」である者
+【C日程に出願する者】出願時に「留学」の在留資格を有する者
+【大学】
+出願資格：
+2024年4月1日以降に実施されたEJU220点以上(読解・聴解・聴読解)、JLPT　N2以上、NAT-TEST2級以上、J-TEST(A-Cレベル600点以上)、JPT 525点以上のいずれか。
+※その他要項は、募集要項に記載のとおり。
+【短期大学】
+※大手前大学に編入希望者であることが前提
+出願資格：
+2024年4月1日以降に実施された以下の試験の通知書の写しを提出した者↓
+N3以上、NAT-TEST3級、J.TEST:D-Eレベル500点以上、JPT430点以上525点未満、PJCレベルD⁺、PJC bridgeレベルA⁺
+↑※これらより上位の資格・点数の者は出願不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>羽衣国際大学</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>各学科／1名／※新学科のみ未定</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>出願資格：次の各項のすべてに該当する者
+①貴校の校長が推薦し、かつ本学を専願とする者
+②外国籍を有し、出入国管理及び難民認定法による「留学」の在留資格を2027年3月31日までに取得可能なもの
+③次のいずれかに該当する者
+1.外国において12年の課程を終了、または2027年3月31日までに修了見込みの者
+2. 1.に準ずるも者で文部科学大臣の指定した者
+3.本学が実施する個別の入学資格審査により、高等学校を卒業した者と同等以上の学力があると認められた18歳以上の者
+推薦基準：
+次の各項のすべてに該当する者
+①貴校における入学時からの出席率が90％以上の者
+②大学入学時に日本語による受講が可能な日本語能力を有する者（下記いずれか）
+【放送メディア映像学】
+・N2以上取得もしくはEJU270点以上
+【現代社会学科＆人間生活学科】
+・N2以上取得もしくはEJU240点以上
+③大学生活を送る上で十分な支弁能力を兼ね備えていると認められる者
+④志望学科の学問分野に深く関心のある者</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>関西国際大学</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>全学部合計4名</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>出願資格
+外国籍を有する者で、（1）出願資格のいずれかに該当し、かつ（2）出願条件と（3）（4）を満たし、本学を専願とする者に出願資格があります。
+（1）出願資格
+次のいすれかに該当する者
+①外国において、学校教育における12年の課程を修了した者または2027年3月31日までに修了見込みの者。ただし、12年課程のうち日本の小学校・中学校・高校に在籍した場合はその期間が通算3年以内に限る。
+②その他、本学が上記と同等以上の学力があると認めた者で、2027年3月31日までに18歳に達する者
+（2）出願条件
+①～⑤のいすれかに該当し、在籍する日本語学校・専門学校の出席率が原則として95％以上の者
+①JLPT　N2以上に合格している者
+②EJU読解、聴解、聴読解の合計が220点以上の者
+③J．TEST　A‐CレベルのC級以上を取得したもの
+④NAT‐TESTの2級以上を取得したもの
+⑤JPT日本語能力試験525点以上を取得した者
+（3）学校長の推薦を受けた者
+（4）在留資格「留学」を取得でき、2027年4月1日に本学に入学可能なもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>相愛大学</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>各学科／前期：5名／後期：若干名</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>【人文学科】
+１～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
+１）外国籍を有し、外国において日本の高等学校卒業に相当する12年の学校教育を修了した者、またはこれに準じる者
+２）日本語学校を2027年度中に卒業した者、または卒業見込みの者で成績優秀でかつ学校長が推薦する者
+３）2027年4月1日現在において満18歳に達した者で、原則として日本居住が3年以内の者
+４）次のa～cいずれかに該当する者
+a)JLPTを受験し、N2以上に合格した者
+b)EJU　EJU240点以上（記述を含む）
+c)本学が実施する「出願資格認定試験」で認定を受けた者
+５）出席率95％以上の者
+６）本学の教育方針を理解し、志望学科に対する明確な志向とそれに相応しい能力・適正を備えた者
+【管理栄養学科】
+１～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
+１）外国籍を有し、外国において日本の高等学校卒業に相当する12年の学校教育を修了した者、またはこれに準じる者
+２）日本語学校を2027年度中に卒業した者、または卒業見込みの者で成績優秀でかつ学校長が推薦する者
+３）2027年4月1日現在において満18歳に達した者で、原則として日本居住が3年以内の者
+４）次のa～cいずれかに該当する者
+a)JLPTを受験し、N2以上に合格した者
+b)EJU　EJU200点以上（記述を含む）
+c)本学が実施する「出願資格認定試験」で認定を受けた者
+５）出席率90％以上の者
+６）本学の教育方針を理解し、志望学科に対する明確な志向とそれに相応しい能力・適正を備えた者</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>大阪経済大学　国際共創部　国際共創学科</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>1名</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>①外国の国籍を有し、外国において学校教育における12年の課程を修了した者、もしくは2027年3月までに修了見込みの者
+※12年の課程のうち、日本の高等学校での在籍期間が3年以内の者も資格を有する。
+②文部科学省令により上記①と同等以上の資格を有する者、もしくは上記①と同等以上の資格を有すると本学が認めた者。
+③本学受験時までに来日して6か月以上経過している者で2027年3月31日までに日本語学校を卒業（修了）見込みの者。
+④「出入国管理及び難民認定法」による「留学」の在留資格を取得または更新できる者。
+⑤JLPT　N2以上またはEJU「日本語（記述問題を含む）」230点以上の者(聴読解及び読解で各100点以上、記述30点以上)。
+⑥本学が推薦を依頼する日本語学校に在学し、その日本語学校学校長が責任をもって推薦する者。
+⑦本学国際共創学部を第1志望とし、強く入学を希望する者（合格すれば、必ず入学する者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>天理大学</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>2名</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>出願資格：
+つぎの１から５のいずれかにも該当する者。
+1．本大学の建学の精神を理解しその趣旨にそう者
+2．本大学の指定する学校を2027年3月修了見込みの者で、出身学校長が推薦し、かつ本大学を専願する者
+3．外国籍を有し、外国において学校教育における12年の課程を修了した者、もしくはこれに準ずる者として文部科学大臣の指定した者
+4．学業を目的として日本に居住し、「出入国管理及び難民認定法」による「留学」の在留資格を有する者またはそれに切り替え可能な在留資格を有する者
+5．本大学の指定する学校在学中の出席率が90％以上の学生で、日本留学試験（日本語）200点以上または日本語能力試験N2程度の日本語能力を有する者
+※出願後の志望専攻の変更は一切認められない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>育英館大学</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>1名</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>出願資格
+①～⑤のすべてを満たす者
+①2027年3月に本学が指定した日本語学校を卒業見込みの者。
+②出席状況が95%以上である者。
+③日本語能力が以下のいずれかである者
+　　・EJUの日本語(読解・聴解・聴読解)の合計点が200点以上
+　　・JLPT N2以上
+④合格した場合に必ず入学する意思のある者。
+⑤学校長の推薦を受けた者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>山梨学院大学</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>2名</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>【推薦条件】
+①本学の入学者選抜に合格した場合、入学意思がある者(専願)
+②誠実で協調性があり勉学意欲が旺盛で、経営学部経営学科の修業に適性のある者。
+③日本語能力試験N2以上に合格した者、または、EJU(日本語/記述除く)200点以上の者。
+④出席率(時間数換算)が85%以上の者。
+⑤本学における4年間の学費・生活費などの支弁が可能である者。
+⑥日本の法律を遵守し、健全な留学生活を送ることが約束できるもの。
+※指定校で受験の場合、入学選抜の筆記試験(日本語総合試験)免除。
+ただし、JLPT N2合格者でCEFR判定がB1の場合、またはEJUの受験年度・回の平均点未満の場合は、推薦書の中に日本語学習の到達度に「CEFR B2 相当の学習をしている」(または卒業時までにB2に達する)旨を記述すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>神戸国際大学</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>（1年入学）各学科1名／（2年編入）1名</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>次の条件を満たすもの
+【1年次入学】
+①外国で高等学校に相当する学校の過程を修了した者
+②日本で日本語学校または、専門学校を2026年3月までに修了見込みの者
+③学校長が推薦するもの
+④本学を専願するもの
+⑤在留資格が出入国管理法の「留学」のもの
+⑥日本語能力がN2相当であるもの（※N2相当は下記いずれかの基準）
+・日本語能力試験（JLPT）N2受験予定のもの
+・日本留学試験日本語（EJU）（記述除く）200点以上のもの
+・実用日本語検定（J₋TEST）A～Cレベル試験600点以上のもの
+・JPT日本語能力試験525点以上のもの
+⑦在籍期間中の出席率が90％以上であるもの
+【編入】
+①日本で日本語学校または、専門学校を2026年3月までに修了見込みの者
+②以下の①～③いずれかに該当するもの
+・日本国内の大学、短期大学または高等学校専門学校を卒業した者
+・日本国内の専修学校専門課程（修業年限が2年以上であること、その他文部科学大臣が定める基準を満たす者に限る）を修了した者
+・日本国外の大学で2年以上の課程を修了した者
+③学校長が推薦するもの
+④本学を専願するもの
+⑤在留資格が出入国管理法の「留学」のもの
+・日本語能力がN2以上を取得しているもの
+・日本留学試験日本語（EJU）450点満点のうち225点以上を取得している
+・実用日本語検定（J₋TEST）A～Cレベル試験600点以上のもの
+・JPT日本語能力試験525点以上のもの
+⑦在籍期間中の出席率が90％以上であるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>桃山学院大学</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>6名</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>【出願資格】以下の全てに該当する者
+(1)日本居住の外国人で、外国において12年の学校教育を修了した者。
+(2)日本語能力試験N2レベル以上の者、またはEJUの日本語科目(読解、聴解及び聴読解)の得点が220点以上の日本語能力を有する者。
+なお工学部工学科を志願する者は、これに加えて、EJUの「数学コース2」の得点が100点以上で、かつ「理科」の得点を有する者。
+(3)専願</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>名古屋経済大学</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>外国籍を有する者で、次の（1）～（5）のすべてに該当する者、または（2）～（6）のすべてに該当する者とする。
 （1）外国において、学校教育における12年の課程を修了した者、もしくはこれに準ずる者で文部科学大臣のしてした者、または高等学校を卒業した者と同等以上の学力があると本学が認めた者
@@ -3995,41 +3948,77 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>追手門学院大学（パートナー校制度）</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>2名</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>【前期】
+・JLPT N3以上
+・EJU180点以上（2025年第二回、2026年第一回）
+・J.TEST A-Cレベル500点以上
+・ビジネス日本語能力テスト420点以上
+・JPT500点以上　いずれかを有する者
+・TOEFL iBT 74以上、IELTS 5.5以上、TOEIC 800以上、Duolingo English Test100以上のいずれかを有する者
+【後期】
+・JLPT N3以上
+・EJU180点以上（2025年第二回、2026年第一回、2026年第二回）
+・J.TEST A-Cレベル500点以上
+・ビジネス日本語能力テスト420点以上
+・JPT500の点以上　いずれかを有する者
+・TOEFL iBT 74以上、IELTS 5.5以上、TOEIC 800以上、Duolingo English Test100以上のいずれかを有する者
+英語能力に応じて最大100%の授業料免除制度あり</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>城西国際大学</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr"/>
+      <c r="D23" s="18" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>太成学院大学</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>１)下記の試験・スコアのいずれか一つ以上を有している方
 ・日本留学試験（EJU）＿220点以上
@@ -4041,22 +4030,22 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>日本工業大学</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>出願条件：
 ①外国籍を有し、外国において学校教育における12年の課程を修了した方、またはこれに準ずる文部科学大臣の指定した方。
@@ -4072,22 +4061,22 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>平安女学院大学</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>（1）本学指定する日本語教育施設で、在籍する学校長の推薦を受けた方。
 （2）外国において学校教育における12年の課程を修了した方、文化科学省が定める大学入学資格に該当する方、または本学においてこれと同等以上の資格を有すると認められる方。
@@ -4100,22 +4089,22 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>駒沢女子大学・短期大学</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>（１）2027年3月に貴校を卒業見込みの者で、人間性に富み、高等教育を受けるのに適した素質と必要な学力をもち学校長が推薦するに値すると認めた者。
 （２）本学への入学を第一希望とし、合格した場合は必ず入学する者（専願）
@@ -4128,22 +4117,22 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>大阪国際大学</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>各1名ずつ</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>【出願資格】
 ①2027年3月に日本語学校を修了見込みのもの
@@ -4156,22 +4145,22 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>近畿大学</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>前期・後期合計／2名</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>下記①～③のいずれかを満たす者
 ①外国に所在する学校で所在国・地域の法令に基づく正規の学校教育における12年目の課程を修了した者または2027年3月までに修了見込みの者
@@ -4186,22 +4175,22 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>神戸学院大学</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>被推薦者の資格
 ①外国において学校教育における12年の課程を修了した者、または、これに準ずる者で文部科学大臣の指定した者。
@@ -4216,22 +4205,22 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>上海大学</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>①募集要項に記載の出願資格を満たしている者
 ・高等学校卒業まはたそれに相当する資格を有すること
@@ -4246,22 +4235,22 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>中日本自動車短期大学（岐阜）</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>以下の条件を全て満たしていること
 ・入国管理及び難民認定法の定めるところにより、在留資格「留学」を有するもの及び取得見込みの者。（技能実習ビザのものは不可）
@@ -4281,22 +4270,22 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>大阪女学院大学</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>●推薦条件（大阪女学院大学・大阪女学院短期大学）
 １）日本語学校用の学校長の推薦を受け、本学で学ぶ意欲のある専願の方
@@ -4319,22 +4308,22 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>大阪キリスト教短期大学</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>介護福祉別科：2名／教育テック：3名</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>以下の条件を満たす者↓
 【介護福祉学科】

--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -1272,58 +1272,152 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>38日</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>名古屋経済大学</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>経済学部現代経済学科、経営学部経営学科、法学部ビジネス法学科</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>N2（B2）レベル相当以上の日本語能力があると認められる者</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>90%以上</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ期　2025年9月30日（水）10:00～10月9日（金）15:00
+Ⅱ期　2025年10月28日（水）10:00～11月4日（水）15:00
+Ⅲ期　2025年11月24日（火）10:00～12月2日（水）15:00
+Ⅳ期　2026年1月5日（火）10:00～1月15日（金）15:00
+Ⅴ期　2026年1月25日（月）10:00～2月5日（金）15:00
+Ⅵ期　2026年2月15日（月）10:00～2月26日（金）15:00
+インターネット出願期間
+※出願書類提出は締め切り日当日消印有効</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ期　10月17日（土）
+Ⅱ期　11月15日（日）
+Ⅲ期　12月12日（土）
+Ⅳ期　2月1日（月）
+Ⅴ期　2月19日（金）
+Ⅵ　3月5日（金）</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ期　11月2日（月）
+Ⅱ期　12月1日（火）
+Ⅲ期　12月18日（金）
+Ⅳ期　2月12日（金）
+Ⅴ期　2月26日（金）
+Ⅵ期　3月11日（木）</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ期　11月19日（木）
+Ⅱ期　12月17日（木）
+Ⅲ期　1月18日（月）
+Ⅳ期　2月24日（水）
+Ⅴ期　3月8日（月）
+Ⅵ期　3月23日（火）</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>書類審査、面接、小論文により、合否を決定します。
+小論文は以下の2題を出題します。解答時間は60分です。
+小論文テーマ
+①事前にテーマ公表「あなたの夢を語ってください。その夢に向けて、名古屋経済大学で何をどのように学ぼうと考えていますか。」（300字～400字）
+②試験当日にテーマ公表、読解作文（200字程度）</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
           <t>43日</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科・経済学部 経済学科・／システム工学部 システム工学科</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>9/14(月)～10/14(水)</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>10/24（土）
 集合時間:12:30
 試験時間:13:00</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>11/1（日）
 10:00～</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>（１次）入学金の納入と手続き書類の提出
 11/2（月）～12/1（火）消印有効
@@ -1331,7 +1425,7 @@
 11/2（月）～12/17（木）</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>エントリーシートに基づく面接
 200点
@@ -1339,46 +1433,46 @@
 しかし、入学試験の結果において、大学の授業に支障があると判断した場合、不合格の可能性あり。</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>44日</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>国際日本・建築&amp;芸術・現代社会・経営／／大手前短期大学／ライフデザイン総合</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>N2以上、NAT-TEST2級以上、J-TEST(A-Cレベル600点以上)、JPT 525点以上のいずれか。</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/10/1(木)～10/15(木)
 B日程：2026/12/14(月)～2027/1/12(火)
@@ -1386,7 +1480,7 @@
 ※消印有効</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>A日程：11/5(木)
 B日程：1/27(水)
@@ -1394,14 +1488,14 @@
 ※試験会場はすべて、西宮夙川キャンパス</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>A日程：11/19(木)
 B日程：2/11(木・祝)
 C日程：3/4(木)</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>入学金納入期日：
 A日程：2025/12/7(月)
@@ -1414,7 +1508,7 @@
 ※詳細は募集要項に記載あり</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>大学
 ①筆記試験 10:00～11:00
@@ -1428,213 +1522,213 @@
 ②個人面接(約15分)</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>45日</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>現代社会学科・放送・メディア映像学科・人間生活学科／（新）デジタルインテリジェンス学科（仮称）</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>各学科／1名／※新学科のみ未定</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>N2以上取得もしくはEJU270点以上</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>前期:9/7(月)～10/16(金)
 後期:2/1(月)～2/15(月)
 ※必着</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>前期:10/24(土)
 後期:2/19(金)</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>前期:11/2(月)
 後期:2/25(木)</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>前期:11/19(木)
 後期:3/4(木)</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>面接（15分）
 ※読み上げ小テスト含む</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>69日</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>情報学部　情報デザイン学科/グローバル学部　グローバル学科/心理学部　心理学科（神戸山手キャンパス）／教育学部　教育福祉学科/経営学部　経営学科（尼崎キャンパス）</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格している者</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>202610月6日（火）～11月9日（月）
 締切日消印有効</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>11月21日（土）</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>12月1日（火）</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>1次手続き入学金20万円　12月17日（木）
 2次手続き授業料等　2027年1月21日（木）</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>個人面接を実施し、出願書類及び指定校推薦書とあわせて総合判定の上、合否を判定します。
 試験は、日本語による個人面接（20分程度）を、尼崎キャンパスにて対面で行います。</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>70日</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>人文学科、管理栄養学科</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>前期　11/1～11/10
 後期　2/3～2/13</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>前期　11/21
 後期　2/22</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>前期　12/1
 後期　3/3</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>前期：入学金納入→12/11
 前期授業料等納入→6/14
@@ -1642,194 +1736,194 @@
 前期授業料等納入→6/15</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>面接
 （推薦書・志望理由書）を参考にする</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>70日</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>N2以上またはEJU「日本語（記述問題を含む）」230点以上の者(聴読解及び読解で各100点以上、記述30点以上)。</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>2026年11月1日（日）～11月10日（火）
 締切日必着（郵送に限ります。速達　簡易書留で送付します）</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>2026年11月21日（土）
 口頭試問:13:00～</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>2026年12月7日（月）
 13：00～</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>入学金・春学期分学費・諸会費の納付期間2026年12月7日（月）～2027年1月29日（金）</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>日本語による口頭試問　配点100点</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>71日</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>国際学部　日本学科（留学生対象）</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>N2程度の日本語能力を有する者</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>2026/11/2(月)～11/11(水)
 ※必着</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>面接：
 2026/11/20(金)
 ※学校長からの推薦書・調査書及び課題論文をもとに「書類審査」・「面接」により選抜します。</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>2026/12/1(火)
 ※「選考結果通知書」は学校宛てに郵送します。
 本人へは、出願時に登録していただくPost@net のマイページから発表します。</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>【第1次】2026/12/15(水)…入学金
 【第2次】2026/1/20(火)…春学期分納付金と入学手続書類＜必着＞</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>推薦書・調査書及び課題論文をもとに
 「書類審査」・「面接」により選抜</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>72日</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>1期：11月2日(月)～11月12日(木)
 Ⅱ期：12月1日(火)～12月16日(水)
@@ -1838,7 +1932,7 @@
 Ⅴ期：2月24日(水)～3月11日(木)</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月14日(土)
 Ⅱ期：12月19日(土)
@@ -1847,7 +1941,7 @@
 Ⅴ期：3月13日(土)</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月18日(水)
 Ⅱ期：12月23日(水)
@@ -1856,7 +1950,7 @@
 Ⅴ期：3月18日(木)</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月26日(木)
 Ⅱ期：1月7日(木)
@@ -1865,56 +1959,56 @@
 Ⅴ期：3月26日(金)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>・書類審査
 ・個人面接(日本語の口頭試問含むオンライン試験)</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>87日</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者、または、EJU(日本語/記述除く)200点以上の者。</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>85%以上</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年11月9日(月)～11月27日(金)
 (WEB出願は24日の午後5時まで)
@@ -1925,21 +2019,21 @@
 いずれも必着締め切り</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月5日(土)
 Ⅱ期：2027年2月7日(日)
 Ⅲ期：2027年2月26日(金)</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月11日(金)
 Ⅱ期：2027年2月12日(金)
 Ⅲ期：2027年3月5日(金)</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2027年1月13日(水)
 Ⅱ期：2027年2月26日(金)
@@ -1947,56 +2041,56 @@
 必着締め切り</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>①出願書類審査(志望理由書、在籍校での成績及び出席率、推薦書を含む)
 ②面接試験(15分)…集団面接</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>90日</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>経済経営学科、国際文化ビジネス・観光学科</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>N2相当であるもの（※N2相当は下記いずれかの基準）</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 【前期】
@@ -2009,21 +2103,21 @@
 窓口の場合は16:00まで</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/13
 後期：2/22</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/24
 後期：3/4</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期
@@ -2034,74 +2128,74 @@
 （第二次）〃</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>書類審査
 本学独自の日本語能力試験
 面接</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>100日</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>国際教養学部 英語・国際文化学科、／社会学部 社会学科/社会福祉学科(※現：ソーシャルデザイン学科で2027年4月に社会福祉学科に名称変更構想中)、／法学部 法律学科、経済学部 経済学科、経営学部 経営学科、工学部 工学科</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>N2レベル以上の者、またはEJUの日本語科目(読解、聴解及び聴読解)の得点が220点以上の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>2026年12月1日(火)～12月10日(木)
 ※入学検定料は締め切り12/11(金)13時振込完了
 締切日当日消印有効</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026/12/19（土）</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>2026/12/24（木）</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>2026年12月24日(木)～
 2027年2月12日(金)
@@ -2109,106 +2203,12 @@
 入学申込金、春学期授業料一括納入</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>・面接
 ・小論文
 ・書類審査
 (EJUの成績確認書またはN２以上の成績証明書)/工学部工学科のみEJUの数学コース2及び理科の成績確認書も</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>名古屋経済大学</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>経済学部現代経済学科、経営学部経営学科、法学部ビジネス法学科</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>専願</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>N2（B2）レベル相当以上の日本語能力があると認められる者</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>90%以上</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Ⅰ期　2025年9月30日（水）10:00～10月9日（金）15:00
-Ⅱ期　2025年10月28日（水）10:00～11月4日（水）15:00
-Ⅲ期　2025年11月24日（火）10:00～12月2日（水）15:00
-Ⅳ期　2026年1月5日（火）10:00～1月15日（金）15:00
-Ⅴ期　2026年1月25日（月）10:00～2月5日（金）15:00
-Ⅵ期　2026年2月15日（月）10:00～2月26日（金）15:00
-インターネット出願期間
-※出願書類提出は締め切り日当日消印有効</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Ⅰ期　10月17日（土）
-Ⅱ期　11月15日（日）
-Ⅲ期　12月12日（土）
-Ⅳ期　2月1日（月）
-Ⅴ期　2月19日（金）
-Ⅵ　3月5日（金）</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Ⅰ期　11月2日（月）
-Ⅱ期　12月1日（火）
-Ⅲ期　12月18日（金）
-Ⅳ期　2月12日（金）
-Ⅴ期　2月26日（金）
-Ⅵ期　3月11日（木）</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Ⅰ期　11月19日（木）
-Ⅱ期　12月17日（木）
-Ⅲ期　1月18日（月）
-Ⅳ期　2月24日（水）
-Ⅴ期　3月8日（月）
-Ⅵ期　3月23日（火）</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>書類審査、面接、小論文により、合否を決定します。
-小論文は以下の2題を出題します。解答時間は60分です。
-小論文テーマ
-①事前にテーマ公表「あなたの夢を語ってください。その夢に向けて、名古屋経済大学で何をどのように学ぼうと考えていますか。」（300字～400字）
-②試験当日にテーマ公表、読解作文（200字程度）</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr"/>
@@ -3545,15 +3545,43 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
+          <t>名古屋経済大学</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>外国籍を有する者で、次の（1）～（5）のすべてに該当する者、または（2）～（6）のすべてに該当する者とする。
+（1）外国において、学校教育における12年の課程を修了した者、もしくはこれに準ずる者で文部科学大臣のしてした者、または高等学校を卒業した者と同等以上の学力があると本学が認めた者
+（2）出入国管理及び難民認定法において、本学入学支障のない在留資格（「留学」、「家族滞在」、「定住等」）が取得できるもの
+（3）独立行政法人国際交流基金と公益財団法人日本国債教育支援協会が実施する日本語能力試験（JLPT）N2（B2）レベル相当以上の日本語能力があると認められる者
+（4）学校長が推薦し本学を専願とする者
+（5）出身学校での出席率が90％以上の者
+（6）学校教育における12年の課程を修了し、外国において9年以上の学校教育を受けたもので、出願時に日本での在留期間が4年未満であるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>①日本国籍を有しない者
 ②下記（1）～（3）のいずれかを満たす者
@@ -3569,23 +3597,23 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>【大学・短大共通条件↓】
 出席率90%以上
@@ -3611,23 +3639,23 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>各学科／1名／※新学科のみ未定</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>出願資格：次の各項のすべてに該当する者
 ①貴校の校長が推薦し、かつ本学を専願とする者
@@ -3649,23 +3677,23 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>出願資格
 外国籍を有する者で、（1）出願資格のいずれかに該当し、かつ（2）出願条件と（3）（4）を満たし、本学を専願とする者に出願資格があります。
@@ -3685,23 +3713,23 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>【人文学科】
 １～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
@@ -3728,23 +3756,23 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>①外国の国籍を有し、外国において学校教育における12年の課程を修了した者、もしくは2027年3月までに修了見込みの者
 ※12年の課程のうち、日本の高等学校での在籍期間が3年以内の者も資格を有する。
@@ -3757,23 +3785,23 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>出願資格：
 つぎの１から５のいずれかにも該当する者。
@@ -3786,23 +3814,23 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>出願資格
 ①～⑤のすべてを満たす者
@@ -3816,23 +3844,23 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>【推薦条件】
 ①本学の入学者選抜に合格した場合、入学意思がある者(専願)
@@ -3846,23 +3874,23 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>次の条件を満たすもの
 【1年次入学】
@@ -3894,57 +3922,29 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>【出願資格】以下の全てに該当する者
 (1)日本居住の外国人で、外国において12年の学校教育を修了した者。
 (2)日本語能力試験N2レベル以上の者、またはEJUの日本語科目(読解、聴解及び聴読解)の得点が220点以上の日本語能力を有する者。
 なお工学部工学科を志願する者は、これに加えて、EJUの「数学コース2」の得点が100点以上で、かつ「理科」の得点を有する者。
 (3)専願</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>名古屋経済大学</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>外国籍を有する者で、次の（1）～（5）のすべてに該当する者、または（2）～（6）のすべてに該当する者とする。
-（1）外国において、学校教育における12年の課程を修了した者、もしくはこれに準ずる者で文部科学大臣のしてした者、または高等学校を卒業した者と同等以上の学力があると本学が認めた者
-（2）出入国管理及び難民認定法において、本学入学支障のない在留資格（「留学」、「家族滞在」、「定住等」）が取得できるもの
-（3）独立行政法人国際交流基金と公益財団法人日本国債教育支援協会が実施する日本語能力試験（JLPT）N2（B2）レベル相当以上の日本語能力があると認められる者
-（4）学校長が推薦し本学を専願とする者
-（5）出身学校での出席率が90％以上の者
-（6）学校教育における12年の課程を修了し、外国において9年以上の学校教育を受けたもので、出願時に日本での在留期間が4年未満であるもの</t>
         </is>
       </c>
     </row>

--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -54,7 +54,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,11 +69,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F0E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBF2DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,22 +132,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,9 +145,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2216,159 +2196,41 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>⚠</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>15日</t>
+          <t>2日</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>追手門学院大学（パートナー校制度）</t>
+          <t>太成学院大学</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>国際学部 国際学科 グローバルスタディーズ専攻</t>
+          <t>健康スポーツ学科、看護学科／心理カウンセリング学科、現代ビジネス学科</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>2名</t>
+          <t>若干名</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr"/>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>日本語要件の記載なし</t>
+          <t>N2（112点以上）またはN1</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>記載なし</t>
+          <t>90%以上</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年9月10日（木）～2026年9月16日（水）
-【後期】2026年12月18日（金）～2027年1月12日（火）
-※当日消印有効</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>前期：2026年10月3日（土）
-後期：2027年1月28日（木）</t>
-        </is>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年10月9日（金）
-【後期】2027年2月18日（木）</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年11月9日（月）
-【後期】2027年2月26日（金）</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="inlineStr">
-        <is>
-          <t>筆記試験（日本語読解・小論文）
-面接（日本語・英語）</t>
-        </is>
-      </c>
-      <c r="N22" s="9" t="inlineStr">
-        <is>
-          <t>募集要項原文は日语组と英语组それぞれに「いずれかを有する者」＝AND。日语 N3 你够，但**必须另有英语成绩**（TOEIC800／IELTS5.5／TOEFL iBT74／Duolingo100 之一）。反面：英語能力に応じて最大100%の授業料免除あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>城西国際大学</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>国際人文学部 国際文化学科/国際交流学科／観光学部 観光学科、経営情報学部 総合経営学科(総合経営コース)／メディア学部 メディア情報学科(ニューメディアコース)、健康科学部 福祉総合学科</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>記載なし</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="9" t="inlineStr"/>
-      <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="9" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr"/>
-      <c r="N23" s="9" t="inlineStr">
-        <is>
-          <t>指定校名单上条件栏是空的、日程也未记载（名单标「編集中」）。学费は官网で確認済（138.7万）だが、出願条件そのものが不明なので判定できない ← 学校の進路担当に確認が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>2日</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>太成学院大学</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>健康スポーツ学科、看護学科／心理カウンセリング学科、現代ビジネス学科</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr"/>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>N2（112点以上）またはN1</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>90%以上</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>A日程：8/24-9/3
 B日程：9/14-10/1
@@ -2376,7 +2238,7 @@
 D日程：1/4-1/28</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>A日程：9/13
 B日程：10/10
@@ -2384,7 +2246,7 @@
 D日程：2/5</t>
         </is>
       </c>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>A日程：9/18
 B日程：10/16
@@ -2392,7 +2254,7 @@
 D日程：2/12</t>
         </is>
       </c>
-      <c r="L24" s="13" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>A日程:
 入学金10/2
@@ -2412,75 +2274,149 @@
 2回目3/16</t>
         </is>
       </c>
-      <c r="M24" s="13" t="inlineStr">
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>面接
 書類</t>
         </is>
       </c>
-      <c r="N24" s="13" t="inlineStr">
+      <c r="N22" s="9" t="inlineStr">
         <is>
           <t>要求 N2 112 分以上，你 111 分差 1 分（EJU220／JPT525／J.TEST C级600 也可以替代）</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>15日</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>追手門学院大学（パートナー校制度）</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>国際学部 国際学科 グローバルスタディーズ専攻</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>2名</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>日本語要件の記載なし</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年9月10日（木）～2026年9月16日（水）
+【後期】2026年12月18日（金）～2027年1月12日（火）
+※当日消印有効</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>前期：2026年10月3日（土）
+後期：2027年1月28日（木）</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年10月9日（金）
+【後期】2027年2月18日（木）</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年11月9日（月）
+【後期】2027年2月26日（金）</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>筆記試験（日本語読解・小論文）
+面接（日本語・英語）</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>募集要項为日语＋英语双条件（AND）：日语N3你够，但必须另持英语成绩证书（TOEIC800／IELTS5.5／TOEFL iBT74／Duolingo100 之一），目前没有证书即不可出愿。（若考出英语成绩则可报，且按英语能力最高100%学费免除；你1月自查时也已将其排除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>30日</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>日本工業大学</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>第１期：2026年9月1日（火）～10月1日（木）必着
 第2期：2026年12月10日(木)～2027年1月19日(火)必着</t>
         </is>
       </c>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>第１期：2026年10月11日（日）
 第２期：2027年1月29日(金)
 場所：日本工業大学埼玉キャンパス</t>
         </is>
       </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>第１期：2026年11月2日（月）
 第2期：2027年2月8日(月)</t>
         </is>
       </c>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>入学金納入
 第1期：2026年11月17日（火）
@@ -2490,136 +2426,136 @@
 第2期：2027年3月9日(火)</t>
         </is>
       </c>
-      <c r="M25" s="13" t="inlineStr">
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>・書類審査（出席・成績証明書、志望理由書、日本留学試験の受験票）
 ・個人面接(15分)。</t>
         </is>
       </c>
-      <c r="N25" s="13" t="inlineStr">
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>必须有 EJU（日语230分，还要考数学课程2）。不认 JLPT</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>31日</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>平安女学院大学</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>国際観光学部　国際観光学科</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>N2以上に合格した方。</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>1期：2026年9/21(月)～10/2(金)
 2期：2027年1/25(月)～2/8(月)</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>1期：2026年10/11(日)13:30～
 2期：2027年2/14(日)13:30～</t>
         </is>
       </c>
-      <c r="K26" s="13" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>1期：2026年10/16(金)
 2期：2027年2/19(金)</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>1期：2026年12/4(金)
 2期：2027年3/12(金)</t>
         </is>
       </c>
-      <c r="M26" s="13" t="inlineStr">
+      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>面接</t>
         </is>
       </c>
-      <c r="N26" s="13" t="inlineStr">
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>42日</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>駒沢女子大学・短期大学</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>国際日本語学科・人間関係学科・心理学科・観光文化学科・空間デザイン学科</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>N2相当の者</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>※入学検定料振込：10:00～15:00
 ※必要書類郵送：最終日消印有効
@@ -2631,7 +2567,7 @@
 Ⅲ₋b期：2/18(木)～2/25(木)</t>
         </is>
       </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Ⅰ₋a期：10/24(土)
 Ⅰ₋b期：11/21(土)
@@ -2641,7 +2577,7 @@
 Ⅲ₋b期：3/10(水)</t>
         </is>
       </c>
-      <c r="K27" s="13" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>Ⅰ₋a期：11/2(月)
 Ⅰ₋b期：12/1(火)
@@ -2651,158 +2587,158 @@
 Ⅲ₋b期：3/12(金)</t>
         </is>
       </c>
-      <c r="L27" s="13" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>‐</t>
         </is>
       </c>
-      <c r="M27" s="13" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>面接（15分程度）
 書類審査</t>
         </is>
       </c>
-      <c r="N27" s="13" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>44日</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>大阪国際大学</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>経営経済学部 経営学科/経済学科、／国際教養学部 国際コミュニケーション学科/国際観光学科</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>各1名ずつ</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>2026年10月5日～10月15日
 （消印有効）</t>
         </is>
       </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>2026-10-24 00:00:00</t>
         </is>
       </c>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>2026-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="L28" s="13" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>入学金〆切：11月6日～11月20日
 前期学費納入〆切：11月6日～12月18日</t>
         </is>
       </c>
-      <c r="M28" s="13" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>書類選考
 面接</t>
         </is>
       </c>
-      <c r="N28" s="13" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>必须有 EJU（日语200分）。不认 JLPT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>135日</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>近畿大学</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>国際学部国際学科グローバル専攻</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>前期・後期合計／2名</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>【前期】2026年8月24日（月）～8月27日（木）
 【後期】2027年1月8日（金）～1月14日（木）</t>
         </is>
       </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>【前期試験】2026年10月10日（土）
 【後期試験】2027年2月20日（土）</t>
         </is>
       </c>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>【前期試験】2026年11月9日（月）
 【後期試験】2027年3月9日（火）</t>
         </is>
       </c>
-      <c r="L29" s="13" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>【前期試験】
 第一次手続：2026年11月9日（月）～11月27日（金）
@@ -2810,207 +2746,207 @@
 【後期試験】2027年3月9日（火）～3月15日（月）</t>
         </is>
       </c>
-      <c r="M29" s="13" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>口頭試問、日本留学試験成績
 総合して合否を判定</t>
         </is>
       </c>
-      <c r="N29" s="13" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>必须有 EJU（日语300分＋综合科目100分＋总分400分）。不认 JLPT</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>135日</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>神戸学院大学</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>グローバル・コミュニケーション学部　グローバル・コミュニケーション学科日本語コース</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>2027年1月6日（水）～1月14日（木）必着</t>
         </is>
       </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>2月10日（水）</t>
         </is>
       </c>
-      <c r="K30" s="13" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>2月19日（金）</t>
         </is>
       </c>
-      <c r="L30" s="13" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>第1次:2月22日（月）～3月1日（月）厳守
 第2次:2月22日（月）～3月8日（月）厳守</t>
         </is>
       </c>
-      <c r="M30" s="13" t="inlineStr">
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>・書類選考
 ・面接
 13:10～</t>
         </is>
       </c>
-      <c r="N30" s="13" t="inlineStr">
+      <c r="N29" s="9" t="inlineStr">
         <is>
           <t>必须有 EJU（日语240分）。不认 JLPT</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>上海大学</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>中国語学部中国語学科</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>日本語要件の記載なし</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>95%以上</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>2026年5月1日～出願終了まで</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>指定校あてに通知</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>指定校あてに通知</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>指定校あてに通知</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>要求中国籍以外，你不符合</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>上海大学</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>中国語学部中国語学科</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>中日本自動車短期大学（岐阜）</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>自動車工学科(2年)・モータースポーツエンジニアリング学科(3年)</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>2名</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>日本語要件の記載なし</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>95%以上</t>
-        </is>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>2026年5月1日～出願終了まで</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>指定校あてに通知</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>指定校あてに通知</t>
-        </is>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>指定校あてに通知</t>
-        </is>
-      </c>
-      <c r="M31" s="13" t="inlineStr">
-        <is>
-          <t>記載なし</t>
-        </is>
-      </c>
-      <c r="N31" s="13" t="inlineStr">
-        <is>
-          <t>要求中国籍以外，你不符合</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>中日本自動車短期大学（岐阜）</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>自動車工学科(2年)・モータースポーツエンジニアリング学科(3年)</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>専願</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>N2程度の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>10月期　9月10日-17日
 11月期　10月15日-22日
@@ -3018,7 +2954,7 @@
 2月期　1月15日-22日</t>
         </is>
       </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>10月期　10月11日
 11月期　11月15日
@@ -3026,7 +2962,7 @@
 2月期　2月7日</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>10月期　10月19日
 11月期　11月23日
@@ -3034,7 +2970,7 @@
 2月期　2月15日</t>
         </is>
       </c>
-      <c r="L32" s="13" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>1次
 10月期　11月13日
@@ -3044,59 +2980,59 @@
 (2次は全て3月15日）</t>
         </is>
       </c>
-      <c r="M32" s="13" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>面接・書類審査</t>
         </is>
       </c>
-      <c r="N32" s="13" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>短期大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>大阪女学院大学</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>大阪女学院大学（3年次編入学）／大阪女学院短期大学／／国際教養学部　国際教養学科</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>共通
 一期：9/24(木)∼9/30(水)
@@ -3107,7 +3043,7 @@
 六期：2027/3/3(水)∼3/9(火)</t>
         </is>
       </c>
-      <c r="J33" s="13" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>共通
 一期：10/11(日)
@@ -3118,7 +3054,7 @@
 六期：2026/3/17(水)</t>
         </is>
       </c>
-      <c r="K33" s="13" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>共通
 一期：10/16(金)
@@ -3129,7 +3065,7 @@
 六期：2027/3/17(水)</t>
         </is>
       </c>
-      <c r="L33" s="13" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>入学金(100,000円納入　書類提出期日)
 一期：11/2(月)
@@ -3147,61 +3083,61 @@
 六期：2025/3/27(火)</t>
         </is>
       </c>
-      <c r="M33" s="13" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>共通
 面接(日本語)約20分
 ※うち3分程度で「日本語と英語をどのように勉強してきたのか、また入学後どのように勉強したいのか」を日本語で発表</t>
         </is>
       </c>
-      <c r="N33" s="13" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>大阪キリスト教短期大学</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>①介護福祉別科／②教育テックコースDXグローバルクラス</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>介護福祉別科：2名／教育テック：3名</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G34" s="13" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>N2 相当またはCEFR B2 以上の日本語力の習得を目指す意志のある者</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年8月7日(金)～8月21日(金)
@@ -3209,7 +3145,7 @@
 2026年8月3日(月)～2026年8月17日(月)</t>
         </is>
       </c>
-      <c r="J34" s="13" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年8月29日(土)
@@ -3217,7 +3153,7 @@
 8月29日（土）</t>
         </is>
       </c>
-      <c r="K34" s="13" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年9月11日(金)
@@ -3225,12 +3161,12 @@
 9月14日（月）</t>
         </is>
       </c>
-      <c r="L34" s="13" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="M34" s="13" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>【介護福祉学科】
 書類審査
@@ -3245,9 +3181,53 @@
 日本語での面接を実施</t>
         </is>
       </c>
-      <c r="N34" s="13" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>短期大学（你指定排除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>城西国際大学</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>国際人文学部 国際文化学科/国際交流学科／観光学部 観光学科、経営情報学部 総合経営学科(総合経営コース)／メディア学部 メディア情報学科(ニューメディアコース)、健康科学部 福祉総合学科</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr"/>
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr"/>
+      <c r="K34" s="9" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr"/>
+      <c r="M34" s="9" t="inlineStr"/>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>学校指定校名单上该校条件栏为空、日程未记载（标注「編集中」）＝当前不存在可执行的出愿路径。（大学官网2026定价138.7万可查，但指定校条件未发布前无法出愿）</t>
         </is>
       </c>
     </row>
@@ -3273,44 +3253,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>学校名</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>枠</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>推薦条件（原文）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>ものつくり大学</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>①外国において学校教育における12年教育の課程を修了したもので、外国の大学入学資格を有するもの
 ②外国において、12年の課程修了相当の学力認定試験に合格したもの
@@ -3326,22 +3306,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>芦屋大学</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>5名</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>推薦条件
 ①大学生活に支障のない経済状況にある者
@@ -3355,22 +3335,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>神戸医療未来大学</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>【姫路キャンパス】／２名／／【大阪天王寺キャンパス】／1名</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>【出願資格】(1～3のいずれかに該当する者)
 (１)外国籍を有し、2027年4月までに18歳に達する者で、本学での授業に支障のない程度(日本語教育の参照枠でB２相当以上)の日本語能力を有すると認められる者。
@@ -3386,22 +3366,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>流通科学大学</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>3名</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>出願資格　
 2027年度外国人留学生入試の出願資格に該当し、本学が指定する日本語学校等を2027年3月に卒業見込みの者で、本学を専願とする者。
@@ -3415,22 +3395,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>京都外国語大学</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>3名／(１学科につき　1名)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>【各学科共通】
 (1)から(7）のすべてに該当する者
@@ -3464,22 +3444,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>大阪経済法科大学</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>前期後期合わせて／計2名／経済学部、経営学部</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>①専願する者
 ②JLPTN2以上、またはEJUにおける日本語（読解・聴読解・聴解）が230点以上の者、または、日本語（読解・聴読解・聴解）が200点以上230点未満の者で、下記のいずれかのスコアを取得している者。
@@ -3490,22 +3470,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>大阪観光大学</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>指定校2名／編入2名</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>①2027年3月卒業見込みで、学校長が推薦したもの。
 ②出席率が90％以上のもの。
@@ -3515,22 +3495,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>園田学園大学</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>5名／5名を超える場合は要相談</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>①授業時間600時間を満たした者かつ、日本語教育の参照枠におけるB2以上の日本語能力を有する者
 ②出席率90％以上</t>
@@ -3538,22 +3518,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>名古屋経済大学</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>外国籍を有する者で、次の（1）～（5）のすべてに該当する者、または（2）～（6）のすべてに該当する者とする。
 （1）外国において、学校教育における12年の課程を修了した者、もしくはこれに準ずる者で文部科学大臣のしてした者、または高等学校を卒業した者と同等以上の学力があると本学が認めた者
@@ -3566,22 +3546,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>①日本国籍を有しない者
 ②下記（1）～（3）のいずれかを満たす者
@@ -3598,22 +3578,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>【大学・短大共通条件↓】
 出席率90%以上
@@ -3640,22 +3620,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>各学科／1名／※新学科のみ未定</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>出願資格：次の各項のすべてに該当する者
 ①貴校の校長が推薦し、かつ本学を専願とする者
@@ -3678,22 +3658,22 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>出願資格
 外国籍を有する者で、（1）出願資格のいずれかに該当し、かつ（2）出願条件と（3）（4）を満たし、本学を専願とする者に出願資格があります。
@@ -3714,22 +3694,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>【人文学科】
 １～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
@@ -3757,22 +3737,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>①外国の国籍を有し、外国において学校教育における12年の課程を修了した者、もしくは2027年3月までに修了見込みの者
 ※12年の課程のうち、日本の高等学校での在籍期間が3年以内の者も資格を有する。
@@ -3786,22 +3766,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>出願資格：
 つぎの１から５のいずれかにも該当する者。
@@ -3815,22 +3795,22 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>出願資格
 ①～⑤のすべてを満たす者
@@ -3845,22 +3825,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>【推薦条件】
 ①本学の入学者選抜に合格した場合、入学意思がある者(専願)
@@ -3875,22 +3855,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>次の条件を満たすもの
 【1年次入学】
@@ -3923,22 +3903,22 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>【出願資格】以下の全てに該当する者
 (1)日本居住の外国人で、外国において12年の学校教育を修了した者。
@@ -3949,22 +3929,49 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>太成学院大学</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>１)下記の試験・スコアのいずれか一つ以上を有している方
+・日本留学試験（EJU）＿220点以上
+・日本語能力試験（JLPT）N2（112点以上）またはN1
+・JPT日本語能力試験＿525点以上
+・実用日本語検定（J.TEST）C級600点以上
+在学期間の出席率が90％以上であり、人物優秀で、本学を強く志望し日本語学校長が推薦する方</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>追手門学院大学（パートナー校制度）</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>【前期】
 ・JLPT N3以上
@@ -3984,68 +3991,23 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>城西国際大学</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>太成学院大学</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>１)下記の試験・スコアのいずれか一つ以上を有している方
-・日本留学試験（EJU）＿220点以上
-・日本語能力試験（JLPT）N2（112点以上）またはN1
-・JPT日本語能力試験＿525点以上
-・実用日本語検定（J.TEST）C級600点以上
-在学期間の出席率が90％以上であり、人物優秀で、本学を強く志望し日本語学校長が推薦する方</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>日本工業大学</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>出願条件：
 ①外国籍を有し、外国において学校教育における12年の課程を修了した方、またはこれに準ずる文部科学大臣の指定した方。
@@ -4060,23 +4022,23 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>平安女学院大学</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>（1）本学指定する日本語教育施設で、在籍する学校長の推薦を受けた方。
 （2）外国において学校教育における12年の課程を修了した方、文化科学省が定める大学入学資格に該当する方、または本学においてこれと同等以上の資格を有すると認められる方。
@@ -4088,23 +4050,23 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>駒沢女子大学・短期大学</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>（１）2027年3月に貴校を卒業見込みの者で、人間性に富み、高等教育を受けるのに適した素質と必要な学力をもち学校長が推薦するに値すると認めた者。
 （２）本学への入学を第一希望とし、合格した場合は必ず入学する者（専願）
@@ -4116,23 +4078,23 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>大阪国際大学</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>各1名ずつ</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>【出願資格】
 ①2027年3月に日本語学校を修了見込みのもの
@@ -4144,23 +4106,23 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>近畿大学</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>前期・後期合計／2名</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>下記①～③のいずれかを満たす者
 ①外国に所在する学校で所在国・地域の法令に基づく正規の学校教育における12年目の課程を修了した者または2027年3月までに修了見込みの者
@@ -4174,23 +4136,23 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>神戸学院大学</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>被推薦者の資格
 ①外国において学校教育における12年の課程を修了した者、または、これに準ずる者で文部科学大臣の指定した者。
@@ -4204,23 +4166,23 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>上海大学</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>①募集要項に記載の出願資格を満たしている者
 ・高等学校卒業まはたそれに相当する資格を有すること
@@ -4234,23 +4196,23 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>中日本自動車短期大学（岐阜）</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>以下の条件を全て満たしていること
 ・入国管理及び難民認定法の定めるところにより、在留資格「留学」を有するもの及び取得見込みの者。（技能実習ビザのものは不可）
@@ -4269,23 +4231,23 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>大阪女学院大学</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>●推薦条件（大阪女学院大学・大阪女学院短期大学）
 １）日本語学校用の学校長の推薦を受け、本学で学ぶ意欲のある専願の方
@@ -4307,23 +4269,23 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>大阪キリスト教短期大学</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>介護福祉別科：2名／教育テック：3名</t>
         </is>
       </c>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>以下の条件を満たす者↓
 【介護福祉学科】
@@ -4343,6 +4305,24 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>城西国際大学</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -54,7 +54,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F0E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3ECF2"/>
       </patternFill>
     </fill>
     <fill>
@@ -103,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -132,10 +137,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -145,6 +159,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1177,28 +1194,32 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>36日</t>
+          <t>38日</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>園田学園大学</t>
+          <t>名古屋経済大学</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>経営学部　ビジネス学科</t>
+          <t>経済学部現代経済学科、経営学部経営学科、法学部ビジネス法学科</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>5名／5名を超える場合は要相談</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>日本語要件の記載なし</t>
+          <t>N2（B2）レベル相当以上の日本語能力があると認められる者</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1207,85 +1228,6 @@
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Ⅰ期　9月28日（月）～10月7日（水）
-Ⅱ期　11月24日（火）～12月9日（水）
-Ⅲ期　1月25日（月）～2月3日（水）
-Ⅳ期　2月15日（月）～3月2日（火）</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Ⅰ期　10月18日（日）10：00
-Ⅱ期　12月20日（日）10：00
-Ⅲ期　2月12日（金）10：00
-Ⅳ期　3月9日（火）10：00</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Ⅰ期　10月23日（金）
-Ⅱ期　12月24日（木）
-Ⅲ期　2月19日（金）
-Ⅳ期　3月12日（金）</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>書類
-面接(10分　100点)
-小論文（10分　100点）</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>38日</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>名古屋経済大学</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>経済学部現代経済学科、経営学部経営学科、法学部ビジネス法学科</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>専願</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>N2（B2）レベル相当以上の日本語能力があると認められる者</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>90%以上</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　2025年9月30日（水）10:00～10月9日（金）15:00
 Ⅱ期　2025年10月28日（水）10:00～11月4日（水）15:00
@@ -1297,7 +1239,7 @@
 ※出願書類提出は締め切り日当日消印有効</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　10月17日（土）
 Ⅱ期　11月15日（日）
@@ -1307,7 +1249,7 @@
 Ⅵ　3月5日（金）</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　11月2日（月）
 Ⅱ期　12月1日（火）
@@ -1317,7 +1259,7 @@
 Ⅵ期　3月11日（木）</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　11月19日（木）
 Ⅱ期　12月17日（木）
@@ -1327,7 +1269,7 @@
 Ⅵ期　3月23日（火）</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>書類審査、面接、小論文により、合否を決定します。
 小論文は以下の2題を出題します。解答時間は60分です。
@@ -1336,68 +1278,68 @@
 ②試験当日にテーマ公表、読解作文（200字程度）</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>43日</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科・経済学部 経済学科・／システム工学部 システム工学科</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>9/14(月)～10/14(水)</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>10/24（土）
 集合時間:12:30
 試験時間:13:00</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>11/1（日）
 10:00～</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>（１次）入学金の納入と手続き書類の提出
 11/2（月）～12/1（火）消印有効
@@ -1405,7 +1347,7 @@
 11/2（月）～12/17（木）</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>エントリーシートに基づく面接
 200点
@@ -1413,46 +1355,46 @@
 しかし、入学試験の結果において、大学の授業に支障があると判断した場合、不合格の可能性あり。</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>44日</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>国際日本・建築&amp;芸術・現代社会・経営／／大手前短期大学／ライフデザイン総合</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>N2以上、NAT-TEST2級以上、J-TEST(A-Cレベル600点以上)、JPT 525点以上のいずれか。</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/10/1(木)～10/15(木)
 B日程：2026/12/14(月)～2027/1/12(火)
@@ -1460,7 +1402,7 @@
 ※消印有効</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>A日程：11/5(木)
 B日程：1/27(水)
@@ -1468,14 +1410,14 @@
 ※試験会場はすべて、西宮夙川キャンパス</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>A日程：11/19(木)
 B日程：2/11(木・祝)
 C日程：3/4(木)</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>入学金納入期日：
 A日程：2025/12/7(月)
@@ -1488,7 +1430,7 @@
 ※詳細は募集要項に記載あり</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>大学
 ①筆記試験 10:00～11:00
@@ -1502,80 +1444,151 @@
 ②個人面接(約15分)</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>45日</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>現代社会学科・放送・メディア映像学科・人間生活学科／（新）デジタルインテリジェンス学科（仮称）</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>各学科／1名／※新学科のみ未定</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>N2以上取得もしくはEJU270点以上</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>前期:9/7(月)～10/16(金)
 後期:2/1(月)～2/15(月)
 ※必着</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>前期:10/24(土)
 後期:2/19(金)</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>前期:11/2(月)
 後期:2/25(木)</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>前期:11/19(木)
 後期:3/4(木)</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>面接（15分）
 ※読み上げ小テスト含む</t>
         </is>
       </c>
+      <c r="N12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>69日</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>関西国際大学</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>情報学部　情報デザイン学科/グローバル学部　グローバル学科/心理学部　心理学科（神戸山手キャンパス）／教育学部　教育福祉学科/経営学部　経営学科（尼崎キャンパス）</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>全学部合計4名</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>N2以上に合格している者</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>95%以上</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>202610月6日（火）～11月9日（月）
+締切日消印有効</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>11月21日（土）</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>12月1日（火）</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>1次手続き入学金20万円　12月17日（木）
+2次手続き授業料等　2027年1月21日（木）</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>個人面接を実施し、出願書類及び指定校推薦書とあわせて総合判定の上、合否を判定します。
+試験は、日本語による個人面接（20分程度）を、尼崎キャンパスにて対面で行います。</t>
+        </is>
+      </c>
       <c r="N13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1586,22 +1599,22 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>69日</t>
+          <t>70日</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>関西国際大学</t>
+          <t>相愛大学</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>情報学部　情報デザイン学科/グローバル学部　グローバル学科/心理学部　心理学科（神戸山手キャンパス）／教育学部　教育福祉学科/経営学部　経営学科（尼崎キャンパス）</t>
+          <t>人文学科、管理栄養学科</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>全学部合計4名</t>
+          <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1611,7 +1624,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>N2以上に合格している者</t>
+          <t>N2以上に合格した者</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1620,95 +1633,24 @@
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>202610月6日（火）～11月9日（月）
-締切日消印有効</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>11月21日（土）</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>12月1日（火）</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>1次手続き入学金20万円　12月17日（木）
-2次手続き授業料等　2027年1月21日（木）</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>個人面接を実施し、出願書類及び指定校推薦書とあわせて総合判定の上、合否を判定します。
-試験は、日本語による個人面接（20分程度）を、尼崎キャンパスにて対面で行います。</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>70日</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>相愛大学</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>人文学科、管理栄養学科</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>各学科／前期：5名／後期：若干名</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>専願</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>N2以上に合格した者</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>95%以上</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>前期　11/1～11/10
 後期　2/3～2/13</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>前期　11/21
 後期　2/22</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>前期　12/1
 後期　3/3</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>前期：入学金納入→12/11
 前期授業料等納入→6/14
@@ -1716,12 +1658,79 @@
 前期授業料等納入→6/15</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>面接
 （推薦書・志望理由書）を参考にする</t>
         </is>
       </c>
+      <c r="N14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>70日</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>大阪経済大学　国際共創部　国際共創学科</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>1名</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N2以上またはEJU「日本語（記述問題を含む）」230点以上の者(聴読解及び読解で各100点以上、記述30点以上)。</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月1日（日）～11月10日（火）
+締切日必着（郵送に限ります。速達　簡易書留で送付します）</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月21日（土）
+口頭試問:13:00～</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2026年12月7日（月）
+13：00～</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>入学金・春学期分学費・諸会費の納付期間2026年12月7日（月）～2027年1月29日（金）</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>日本語による口頭試問　配点100点</t>
+        </is>
+      </c>
       <c r="N15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1732,18 +1741,22 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>70日</t>
+          <t>71日</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>大阪経済大学　国際共創部　国際共創学科</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
+          <t>天理大学</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>国際学部　日本学科（留学生対象）</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1名</t>
+          <t>2名</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1753,157 +1766,86 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>N2以上またはEJU「日本語（記述問題を含む）」230点以上の者(聴読解及び読解で各100点以上、記述30点以上)。</t>
+          <t>N2程度の日本語能力を有する者</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>記載なし</t>
+          <t>90%以上</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>2026年11月1日（日）～11月10日（火）
-締切日必着（郵送に限ります。速達　簡易書留で送付します）</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>2026年11月21日（土）
-口頭試問:13:00～</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>2026年12月7日（月）
-13：00～</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>入学金・春学期分学費・諸会費の納付期間2026年12月7日（月）～2027年1月29日（金）</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>日本語による口頭試問　配点100点</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>71日</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>天理大学</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>国際学部　日本学科（留学生対象）</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>専願</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>N2程度の日本語能力を有する者</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>90%以上</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>2026/11/2(月)～11/11(水)
 ※必着</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>面接：
 2026/11/20(金)
 ※学校長からの推薦書・調査書及び課題論文をもとに「書類審査」・「面接」により選抜します。</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>2026/12/1(火)
 ※「選考結果通知書」は学校宛てに郵送します。
 本人へは、出願時に登録していただくPost@net のマイページから発表します。</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>【第1次】2026/12/15(水)…入学金
 【第2次】2026/1/20(火)…春学期分納付金と入学手続書類＜必着＞</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>推薦書・調査書及び課題論文をもとに
 「書類審査」・「面接」により選抜</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>72日</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>1期：11月2日(月)～11月12日(木)
 Ⅱ期：12月1日(火)～12月16日(水)
@@ -1912,7 +1854,7 @@
 Ⅴ期：2月24日(水)～3月11日(木)</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月14日(土)
 Ⅱ期：12月19日(土)
@@ -1921,7 +1863,7 @@
 Ⅴ期：3月13日(土)</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月18日(水)
 Ⅱ期：12月23日(水)
@@ -1930,7 +1872,7 @@
 Ⅴ期：3月18日(木)</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月26日(木)
 Ⅱ期：1月7日(木)
@@ -1939,56 +1881,56 @@
 Ⅴ期：3月26日(金)</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>・書類審査
 ・個人面接(日本語の口頭試問含むオンライン試験)</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>87日</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者、または、EJU(日本語/記述除く)200点以上の者。</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>85%以上</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年11月9日(月)～11月27日(金)
 (WEB出願は24日の午後5時まで)
@@ -1999,21 +1941,21 @@
 いずれも必着締め切り</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月5日(土)
 Ⅱ期：2027年2月7日(日)
 Ⅲ期：2027年2月26日(金)</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月11日(金)
 Ⅱ期：2027年2月12日(金)
 Ⅲ期：2027年3月5日(金)</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2027年1月13日(水)
 Ⅱ期：2027年2月26日(金)
@@ -2021,56 +1963,56 @@
 必着締め切り</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>①出願書類審査(志望理由書、在籍校での成績及び出席率、推薦書を含む)
 ②面接試験(15分)…集団面接</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>90日</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>経済経営学科、国際文化ビジネス・観光学科</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>N2相当であるもの（※N2相当は下記いずれかの基準）</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 【前期】
@@ -2083,21 +2025,21 @@
 窓口の場合は16:00まで</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/13
 後期：2/22</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/24
 後期：3/4</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期
@@ -2108,74 +2050,74 @@
 （第二次）〃</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>書類審査
 本学独自の日本語能力試験
 面接</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>100日</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>国際教養学部 英語・国際文化学科、／社会学部 社会学科/社会福祉学科(※現：ソーシャルデザイン学科で2027年4月に社会福祉学科に名称変更構想中)、／法学部 法律学科、経済学部 経済学科、経営学部 経営学科、工学部 工学科</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>N2レベル以上の者、またはEJUの日本語科目(読解、聴解及び聴読解)の得点が220点以上の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>2026年12月1日(火)～12月10日(木)
 ※入学検定料は締め切り12/11(金)13時振込完了
 締切日当日消印有効</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026/12/19（土）</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>2026/12/24（木）</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>2026年12月24日(木)～
 2027年2月12日(金)
@@ -2183,7 +2125,7 @@
 入学申込金、春学期授業料一括納入</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>・面接
 ・小論文
@@ -2191,46 +2133,120 @@
 (EJUの成績確認書またはN２以上の成績証明書)/工学部工学科のみEJUの数学コース2及び理科の成績確認書も</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>◇</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>15日</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>追手門学院大学（パートナー校制度）</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>国際学部 国際学科 グローバルスタディーズ専攻</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>2名</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>日本語要件の記載なし</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年9月10日（木）～2026年9月16日（水）
+【後期】2026年12月18日（金）～2027年1月12日（火）
+※当日消印有効</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>前期：2026年10月3日（土）
+後期：2027年1月28日（木）</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年10月9日（金）
+【後期】2027年2月18日（木）</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>【前期】2026年11月9日（月）
+【後期】2027年2月26日（金）</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>筆記試験（日本語読解・小論文）
+面接（日本語・英語）</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>条件卡：需先取得英语成绩证书之一（TOEIC800／IELTS5.5／TOEFL iBT74／Duolingo100）。最快路径 Duolingo English Test（在家考、48小时出分、出分后可选择不发送）。拿到成绩即为全池唯一非专愿紫卡，且按英语能力最高100%学费免除</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>太成学院大学</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>健康スポーツ学科、看護学科／心理カウンセリング学科、現代ビジネス学科</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr"/>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>N2（112点以上）またはN1</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>A日程：8/24-9/3
 B日程：9/14-10/1
@@ -2238,7 +2254,7 @@
 D日程：1/4-1/28</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>A日程：9/13
 B日程：10/10
@@ -2246,7 +2262,7 @@
 D日程：2/5</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="12" t="inlineStr">
         <is>
           <t>A日程：9/18
 B日程：10/16
@@ -2254,7 +2270,7 @@
 D日程：2/12</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L22" s="12" t="inlineStr">
         <is>
           <t>A日程:
 入学金10/2
@@ -2274,149 +2290,75 @@
 2回目3/16</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="12" t="inlineStr">
         <is>
           <t>面接
 書類</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr">
+      <c r="N22" s="12" t="inlineStr">
         <is>
           <t>要求 N2 112 分以上，你 111 分差 1 分（EJU220／JPT525／J.TEST C级600 也可以替代）</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>15日</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>追手門学院大学（パートナー校制度）</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>国際学部 国際学科 グローバルスタディーズ専攻</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>30日</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>日本工業大学</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr"/>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>１名</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>記載なし</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年9月10日（木）～2026年9月16日（水）
-【後期】2026年12月18日（金）～2027年1月12日（火）
-※当日消印有効</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>前期：2026年10月3日（土）
-後期：2027年1月28日（木）</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年10月9日（金）
-【後期】2027年2月18日（木）</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>【前期】2026年11月9日（月）
-【後期】2027年2月26日（金）</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>筆記試験（日本語読解・小論文）
-面接（日本語・英語）</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
-        <is>
-          <t>募集要項为日语＋英语双条件（AND）：日语N3你够，但必须另持英语成绩证书（TOEIC800／IELTS5.5／TOEFL iBT74／Duolingo100 之一），目前没有证书即不可出愿。（若考出英语成绩则可报，且按英语能力最高100%学费免除；你1月自查时也已将其排除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>30日</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>日本工業大学</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>１名</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>専願</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>日本語要件の記載なし</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>第１期：2026年9月1日（火）～10月1日（木）必着
 第2期：2026年12月10日(木)～2027年1月19日(火)必着</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>第１期：2026年10月11日（日）
 第２期：2027年1月29日(金)
 場所：日本工業大学埼玉キャンパス</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K23" s="12" t="inlineStr">
         <is>
           <t>第１期：2026年11月2日（月）
 第2期：2027年2月8日(月)</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="L23" s="12" t="inlineStr">
         <is>
           <t>入学金納入
 第1期：2026年11月17日（火）
@@ -2426,136 +2368,215 @@
 第2期：2027年3月9日(火)</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M23" s="12" t="inlineStr">
         <is>
           <t>・書類審査（出席・成績証明書、志望理由書、日本留学試験の受験票）
 ・個人面接(15分)。</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr">
+      <c r="N23" s="12" t="inlineStr">
         <is>
           <t>必须有 EJU（日语230分，还要考数学课程2）。不认 JLPT</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>31日</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>平安女学院大学</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>国際観光学部　国際観光学科</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>N2以上に合格した方。</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>1期：2026年9/21(月)～10/2(金)
 2期：2027年1/25(月)～2/8(月)</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>1期：2026年10/11(日)13:30～
 2期：2027年2/14(日)13:30～</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>1期：2026年10/16(金)
 2期：2027年2/19(金)</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>1期：2026年12/4(金)
 2期：2027年3/12(金)</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="M24" s="12" t="inlineStr">
         <is>
           <t>面接</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="N24" s="12" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>36日</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>園田学園大学</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>経営学部　ビジネス学科</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>5名／5名を超える場合は要相談</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr"/>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>日本語要件の記載なし</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>90%以上</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Ⅰ期　9月28日（月）～10月7日（水）
+Ⅱ期　11月24日（火）～12月9日（水）
+Ⅲ期　1月25日（月）～2月3日（水）
+Ⅳ期　2月15日（月）～3月2日（火）</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>Ⅰ期　10月18日（日）10：00
+Ⅱ期　12月20日（日）10：00
+Ⅲ期　2月12日（金）10：00
+Ⅳ期　3月9日（火）10：00</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>Ⅰ期　10月23日（金）
+Ⅱ期　12月24日（木）
+Ⅲ期　2月19日（金）
+Ⅳ期　3月12日（金）</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>書類
+面接(10分　100点)
+小論文（10分　100点）</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>女子大学实质（2025年4月才由园田学园女子大学改制共学，在校生构成仍是女子大延续）——按你的短大·女大指定排除</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>42日</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>駒沢女子大学・短期大学</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>国際日本語学科・人間関係学科・心理学科・観光文化学科・空間デザイン学科</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>N2相当の者</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>※入学検定料振込：10:00～15:00
 ※必要書類郵送：最終日消印有効
@@ -2567,7 +2588,7 @@
 Ⅲ₋b期：2/18(木)～2/25(木)</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>Ⅰ₋a期：10/24(土)
 Ⅰ₋b期：11/21(土)
@@ -2577,7 +2598,7 @@
 Ⅲ₋b期：3/10(水)</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="12" t="inlineStr">
         <is>
           <t>Ⅰ₋a期：11/2(月)
 Ⅰ₋b期：12/1(火)
@@ -2587,158 +2608,158 @@
 Ⅲ₋b期：3/12(金)</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>‐</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="M26" s="12" t="inlineStr">
         <is>
           <t>面接（15分程度）
 書類審査</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr">
+      <c r="N26" s="12" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>44日</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>大阪国際大学</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>経営経済学部 経営学科/経済学科、／国際教養学部 国際コミュニケーション学科/国際観光学科</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>各1名ずつ</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>2026年10月5日～10月15日
 （消印有効）</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>2026-10-24 00:00:00</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="12" t="inlineStr">
         <is>
           <t>2026-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="L27" s="12" t="inlineStr">
         <is>
           <t>入学金〆切：11月6日～11月20日
 前期学費納入〆切：11月6日～12月18日</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="M27" s="12" t="inlineStr">
         <is>
           <t>書類選考
 面接</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr">
+      <c r="N27" s="12" t="inlineStr">
         <is>
           <t>必须有 EJU（日语200分）。不认 JLPT</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>135日</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>近畿大学</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>国際学部国際学科グローバル専攻</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>前期・後期合計／2名</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>【前期】2026年8月24日（月）～8月27日（木）
 【後期】2027年1月8日（金）～1月14日（木）</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>【前期試験】2026年10月10日（土）
 【後期試験】2027年2月20日（土）</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>【前期試験】2026年11月9日（月）
 【後期試験】2027年3月9日（火）</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="L28" s="12" t="inlineStr">
         <is>
           <t>【前期試験】
 第一次手続：2026年11月9日（月）～11月27日（金）
@@ -2746,207 +2767,207 @@
 【後期試験】2027年3月9日（火）～3月15日（月）</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="M28" s="12" t="inlineStr">
         <is>
           <t>口頭試問、日本留学試験成績
 総合して合否を判定</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr">
+      <c r="N28" s="12" t="inlineStr">
         <is>
           <t>必须有 EJU（日语300分＋综合科目100分＋总分400分）。不认 JLPT</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>135日</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>神戸学院大学</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>グローバル・コミュニケーション学部　グローバル・コミュニケーション学科日本語コース</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>2027年1月6日（水）～1月14日（木）必着</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>2月10日（水）</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="12" t="inlineStr">
         <is>
           <t>2月19日（金）</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="L29" s="12" t="inlineStr">
         <is>
           <t>第1次:2月22日（月）～3月1日（月）厳守
 第2次:2月22日（月）～3月8日（月）厳守</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="M29" s="12" t="inlineStr">
         <is>
           <t>・書類選考
 ・面接
 13:10～</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr">
+      <c r="N29" s="12" t="inlineStr">
         <is>
           <t>必须有 EJU（日语240分）。不认 JLPT</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>上海大学</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>中国語学部中国語学科</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>2026年5月1日～出願終了まで</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="12" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="M30" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr">
+      <c r="N30" s="12" t="inlineStr">
         <is>
           <t>要求中国籍以外，你不符合</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>中日本自動車短期大学（岐阜）</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>自動車工学科(2年)・モータースポーツエンジニアリング学科(3年)</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>N2程度の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>10月期　9月10日-17日
 11月期　10月15日-22日
@@ -2954,7 +2975,7 @@
 2月期　1月15日-22日</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>10月期　10月11日
 11月期　11月15日
@@ -2962,7 +2983,7 @@
 2月期　2月7日</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="12" t="inlineStr">
         <is>
           <t>10月期　10月19日
 11月期　11月23日
@@ -2970,7 +2991,7 @@
 2月期　2月15日</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="L31" s="12" t="inlineStr">
         <is>
           <t>1次
 10月期　11月13日
@@ -2980,59 +3001,59 @@
 (2次は全て3月15日）</t>
         </is>
       </c>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="M31" s="12" t="inlineStr">
         <is>
           <t>面接・書類審査</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="N31" s="12" t="inlineStr">
         <is>
           <t>短期大学（你指定排除）</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>大阪女学院大学</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>大阪女学院大学（3年次編入学）／大阪女学院短期大学／／国際教養学部　国際教養学科</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
         <is>
           <t>共通
 一期：9/24(木)∼9/30(水)
@@ -3043,7 +3064,7 @@
 六期：2027/3/3(水)∼3/9(火)</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>共通
 一期：10/11(日)
@@ -3054,7 +3075,7 @@
 六期：2026/3/17(水)</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>共通
 一期：10/16(金)
@@ -3065,7 +3086,7 @@
 六期：2027/3/17(水)</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="L32" s="12" t="inlineStr">
         <is>
           <t>入学金(100,000円納入　書類提出期日)
 一期：11/2(月)
@@ -3083,61 +3104,61 @@
 六期：2025/3/27(火)</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="M32" s="12" t="inlineStr">
         <is>
           <t>共通
 面接(日本語)約20分
 ※うち3分程度で「日本語と英語をどのように勉強してきたのか、また入学後どのように勉強したいのか」を日本語で発表</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="N32" s="12" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>大阪キリスト教短期大学</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>①介護福祉別科／②教育テックコースDXグローバルクラス</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>介護福祉別科：2名／教育テック：3名</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>N2 相当またはCEFR B2 以上の日本語力の習得を目指す意志のある者</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年8月7日(金)～8月21日(金)
@@ -3145,7 +3166,7 @@
 2026年8月3日(月)～2026年8月17日(月)</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年8月29日(土)
@@ -3153,7 +3174,7 @@
 8月29日（土）</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年9月11日(金)
@@ -3161,12 +3182,12 @@
 9月14日（月）</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="M33" s="12" t="inlineStr">
         <is>
           <t>【介護福祉学科】
 書類審査
@@ -3181,51 +3202,51 @@
 日本語での面接を実施</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr">
+      <c r="N33" s="12" t="inlineStr">
         <is>
           <t>短期大学（你指定排除）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>城西国際大学</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>国際人文学部 国際文化学科/国際交流学科／観光学部 観光学科、経営情報学部 総合経営学科(総合経営コース)／メディア学部 メディア情報学科(ニューメディアコース)、健康科学部 福祉総合学科</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr"/>
+      <c r="G34" s="12" t="inlineStr"/>
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr"/>
-      <c r="J34" s="9" t="inlineStr"/>
-      <c r="K34" s="9" t="inlineStr"/>
-      <c r="L34" s="9" t="inlineStr"/>
-      <c r="M34" s="9" t="inlineStr"/>
-      <c r="N34" s="9" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr"/>
+      <c r="J34" s="12" t="inlineStr"/>
+      <c r="K34" s="12" t="inlineStr"/>
+      <c r="L34" s="12" t="inlineStr"/>
+      <c r="M34" s="12" t="inlineStr"/>
+      <c r="N34" s="12" t="inlineStr">
         <is>
           <t>学校指定校名单上该校条件栏为空、日程未记载（标注「編集中」）＝当前不存在可执行的出愿路径。（大学官网2026定价138.7万可查，但指定校条件未发布前无法出愿）</t>
         </is>
@@ -3253,44 +3274,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>学校名</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>枠</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>推薦条件（原文）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>ものつくり大学</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>①外国において学校教育における12年教育の課程を修了したもので、外国の大学入学資格を有するもの
 ②外国において、12年の課程修了相当の学力認定試験に合格したもの
@@ -3306,22 +3327,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>芦屋大学</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>5名</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>推薦条件
 ①大学生活に支障のない経済状況にある者
@@ -3335,22 +3356,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>神戸医療未来大学</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>【姫路キャンパス】／２名／／【大阪天王寺キャンパス】／1名</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>【出願資格】(1～3のいずれかに該当する者)
 (１)外国籍を有し、2027年4月までに18歳に達する者で、本学での授業に支障のない程度(日本語教育の参照枠でB２相当以上)の日本語能力を有すると認められる者。
@@ -3366,22 +3387,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>流通科学大学</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>3名</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>出願資格　
 2027年度外国人留学生入試の出願資格に該当し、本学が指定する日本語学校等を2027年3月に卒業見込みの者で、本学を専願とする者。
@@ -3395,22 +3416,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>京都外国語大学</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>3名／(１学科につき　1名)</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>【各学科共通】
 (1)から(7）のすべてに該当する者
@@ -3444,22 +3465,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>大阪経済法科大学</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>前期後期合わせて／計2名／経済学部、経営学部</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>①専願する者
 ②JLPTN2以上、またはEJUにおける日本語（読解・聴読解・聴解）が230点以上の者、または、日本語（読解・聴読解・聴解）が200点以上230点未満の者で、下記のいずれかのスコアを取得している者。
@@ -3470,22 +3491,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>大阪観光大学</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>指定校2名／編入2名</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>①2027年3月卒業見込みで、学校長が推薦したもの。
 ②出席率が90％以上のもの。
@@ -3495,45 +3516,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>園田学園大学</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>5名／5名を超える場合は要相談</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>①授業時間600時間を満たした者かつ、日本語教育の参照枠におけるB2以上の日本語能力を有する者
-②出席率90％以上</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>名古屋経済大学</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>外国籍を有する者で、次の（1）～（5）のすべてに該当する者、または（2）～（6）のすべてに該当する者とする。
 （1）外国において、学校教育における12年の課程を修了した者、もしくはこれに準ずる者で文部科学大臣のしてした者、または高等学校を卒業した者と同等以上の学力があると本学が認めた者
@@ -3545,23 +3543,23 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>①日本国籍を有しない者
 ②下記（1）～（3）のいずれかを満たす者
@@ -3577,23 +3575,23 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>【大学・短大共通条件↓】
 出席率90%以上
@@ -3619,23 +3617,23 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>各学科／1名／※新学科のみ未定</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>出願資格：次の各項のすべてに該当する者
 ①貴校の校長が推薦し、かつ本学を専願とする者
@@ -3657,23 +3655,23 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>出願資格
 外国籍を有する者で、（1）出願資格のいずれかに該当し、かつ（2）出願条件と（3）（4）を満たし、本学を専願とする者に出願資格があります。
@@ -3693,23 +3691,23 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>【人文学科】
 １～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
@@ -3736,23 +3734,23 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>①外国の国籍を有し、外国において学校教育における12年の課程を修了した者、もしくは2027年3月までに修了見込みの者
 ※12年の課程のうち、日本の高等学校での在籍期間が3年以内の者も資格を有する。
@@ -3765,23 +3763,23 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>出願資格：
 つぎの１から５のいずれかにも該当する者。
@@ -3794,23 +3792,23 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>出願資格
 ①～⑤のすべてを満たす者
@@ -3824,23 +3822,23 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>【推薦条件】
 ①本学の入学者選抜に合格した場合、入学意思がある者(専願)
@@ -3854,23 +3852,23 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>次の条件を満たすもの
 【1年次入学】
@@ -3902,23 +3900,23 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>【出願資格】以下の全てに該当する者
 (1)日本居住の外国人で、外国において12年の学校教育を修了した者。
@@ -3928,50 +3926,23 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>太成学院大学</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>１)下記の試験・スコアのいずれか一つ以上を有している方
-・日本留学試験（EJU）＿220点以上
-・日本語能力試験（JLPT）N2（112点以上）またはN1
-・JPT日本語能力試験＿525点以上
-・実用日本語検定（J.TEST）C級600点以上
-在学期間の出席率が90％以上であり、人物優秀で、本学を強く志望し日本語学校長が推薦する方</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>◇</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>追手門学院大学（パートナー校制度）</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>【前期】
 ・JLPT N3以上
@@ -3991,23 +3962,50 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>太成学院大学</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>１)下記の試験・スコアのいずれか一つ以上を有している方
+・日本留学試験（EJU）＿220点以上
+・日本語能力試験（JLPT）N2（112点以上）またはN1
+・JPT日本語能力試験＿525点以上
+・実用日本語検定（J.TEST）C級600点以上
+在学期間の出席率が90％以上であり、人物優秀で、本学を強く志望し日本語学校長が推薦する方</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>日本工業大学</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>出願条件：
 ①外国籍を有し、外国において学校教育における12年の課程を修了した方、またはこれに準ずる文部科学大臣の指定した方。
@@ -4022,23 +4020,23 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>平安女学院大学</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>（1）本学指定する日本語教育施設で、在籍する学校長の推薦を受けた方。
 （2）外国において学校教育における12年の課程を修了した方、文化科学省が定める大学入学資格に該当する方、または本学においてこれと同等以上の資格を有すると認められる方。
@@ -4050,23 +4048,46 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>園田学園大学</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>5名／5名を超える場合は要相談</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>①授業時間600時間を満たした者かつ、日本語教育の参照枠におけるB2以上の日本語能力を有する者
+②出席率90％以上</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>駒沢女子大学・短期大学</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>（１）2027年3月に貴校を卒業見込みの者で、人間性に富み、高等教育を受けるのに適した素質と必要な学力をもち学校長が推薦するに値すると認めた者。
 （２）本学への入学を第一希望とし、合格した場合は必ず入学する者（専願）
@@ -4079,22 +4100,22 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>大阪国際大学</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>各1名ずつ</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>【出願資格】
 ①2027年3月に日本語学校を修了見込みのもの
@@ -4107,22 +4128,22 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>近畿大学</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>前期・後期合計／2名</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>下記①～③のいずれかを満たす者
 ①外国に所在する学校で所在国・地域の法令に基づく正規の学校教育における12年目の課程を修了した者または2027年3月までに修了見込みの者
@@ -4137,22 +4158,22 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>神戸学院大学</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>被推薦者の資格
 ①外国において学校教育における12年の課程を修了した者、または、これに準ずる者で文部科学大臣の指定した者。
@@ -4167,22 +4188,22 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>上海大学</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="18" t="inlineStr">
         <is>
           <t>①募集要項に記載の出願資格を満たしている者
 ・高等学校卒業まはたそれに相当する資格を有すること
@@ -4197,22 +4218,22 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>中日本自動車短期大学（岐阜）</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>以下の条件を全て満たしていること
 ・入国管理及び難民認定法の定めるところにより、在留資格「留学」を有するもの及び取得見込みの者。（技能実習ビザのものは不可）
@@ -4232,22 +4253,22 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>大阪女学院大学</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>●推薦条件（大阪女学院大学・大阪女学院短期大学）
 １）日本語学校用の学校長の推薦を受け、本学で学ぶ意欲のある専願の方
@@ -4270,22 +4291,22 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>大阪キリスト教短期大学</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>介護福祉別科：2名／教育テック：3名</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>以下の条件を満たす者↓
 【介護福祉学科】
@@ -4306,22 +4327,22 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>城西国際大学</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr"/>
+      <c r="D34" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>9日</t>
+          <t>8日</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>17日</t>
+          <t>16日</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>24日</t>
+          <t>23日</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>27日</t>
+          <t>26日</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -943,9 +943,9 @@
           <t>◎</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>31日</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>30日</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1013,9 +1013,9 @@
           <t>◎</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>31日</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>30日</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>36日</t>
+          <t>35日</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>38日</t>
+          <t>37日</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>43日</t>
+          <t>42日</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>44日</t>
+          <t>43日</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>45日</t>
+          <t>44日</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>69日</t>
+          <t>68日</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>70日</t>
+          <t>69日</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>70日</t>
+          <t>69日</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>71日</t>
+          <t>70日</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>72日</t>
+          <t>71日</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>87日</t>
+          <t>86日</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>90日</t>
+          <t>89日</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>100日</t>
+          <t>99日</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>15日</t>
+          <t>14日</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>2日</t>
+          <t>1日</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>29日</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -2386,9 +2386,9 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>31日</t>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>30日</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>36日</t>
+          <t>35日</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>42日</t>
+          <t>41日</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>44日</t>
+          <t>43日</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>135日</t>
+          <t>134日</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>135日</t>
+          <t>134日</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">

--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>8日</t>
+          <t>6日</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>16日</t>
+          <t>14日</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>23日</t>
+          <t>21日</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>26日</t>
+          <t>24日</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>28日</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>28日</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>35日</t>
+          <t>33日</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>37日</t>
+          <t>35日</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>42日</t>
+          <t>40日</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>43日</t>
+          <t>41日</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>44日</t>
+          <t>42日</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>68日</t>
+          <t>66日</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>69日</t>
+          <t>67日</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>69日</t>
+          <t>67日</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>70日</t>
+          <t>68日</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>71日</t>
+          <t>69日</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>86日</t>
+          <t>84日</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>89日</t>
+          <t>87日</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>99日</t>
+          <t>97日</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>14日</t>
+          <t>12日</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>1日</t>
+          <t>27日</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>29日</t>
+          <t>27日</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>28日</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>35日</t>
+          <t>33日</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>41日</t>
+          <t>39日</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>43日</t>
+          <t>41日</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>134日</t>
+          <t>132日</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>134日</t>
+          <t>132日</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">

--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>6日</t>
+          <t>5日</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>14日</t>
+          <t>13日</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>21日</t>
+          <t>20日</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>24日</t>
+          <t>23日</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>28日</t>
+          <t>27日</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>28日</t>
+          <t>27日</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>33日</t>
+          <t>32日</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>35日</t>
+          <t>34日</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>40日</t>
+          <t>39日</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>41日</t>
+          <t>40日</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>42日</t>
+          <t>41日</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>66日</t>
+          <t>65日</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>67日</t>
+          <t>66日</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>67日</t>
+          <t>66日</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>68日</t>
+          <t>67日</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>69日</t>
+          <t>68日</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>84日</t>
+          <t>83日</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>87日</t>
+          <t>86日</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>97日</t>
+          <t>96日</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>12日</t>
+          <t>11日</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>27日</t>
+          <t>26日</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>27日</t>
+          <t>26日</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>28日</t>
+          <t>27日</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>33日</t>
+          <t>32日</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>39日</t>
+          <t>38日</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>41日</t>
+          <t>40日</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>132日</t>
+          <t>131日</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>132日</t>
+          <t>131日</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">

--- a/指定校推薦_出願候補.xlsx
+++ b/指定校推薦_出願候補.xlsx
@@ -11,7 +11,7 @@
     <sheet name="条件全文" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'出願候補'!$A$1:$N$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'出願候補'!$A$1:$N$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -708,36 +708,210 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>5日</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>愛知産業大学</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>造形学部　建築学科</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>複数名</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>N2以上に合格している者</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>90%以上</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>【Ⅰ期】
+ネット出願期間：9月1日～9月10日
+書類必着日：9月14日
+【Ⅱ期】
+ネット出願期間：11月13日～12月2日
+書類必着日：12月4日</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>【Ⅰ期】
+9月19日(土)
+【Ⅱ期】
+12月12日(土)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>【Ⅰ期】
+11月1日(日)
+【Ⅱ期】
+12月23日(水)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>5日</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>大阪人間科学大学</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>人間科学部　社会創造学科</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>N2またはJPT 525点以上、CEFR B2以上、EJU 200点以上と同程度の能力を有する者（N2を満たさない者は入試広報センターへ申し出ること）</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>90%以上</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>1期　8月25日-9月10日
+2期　9月18日-10月1日
+3期　10月9日-10月22日
+4期　10月23日-11月1日
+5期　10月23日-11月5日
+6期　11月13日-11月26日
+7期　2027年 1月5日-1月14日
+8期　2027年 1月15日-1月28日
+9期　2027年 2月12日-2月25日
+(消印有効)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>1期　9月19日10:00～
+2期　10月10日10:00～
+3期　10月31日10:00～
+4期　11月7日10:00～
+5期　11月14日10:00～
+6期　12月5日10:00～
+7期　2027年 1月23日10:00～
+8期　2027年 2月6日10:00～
+9期　2027年 3月6日10:00～</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>1期　9月24日
+2期　10月15日
+3期　11月5日
+4期　11月12日
+5期　11月19日
+6期　12月10日
+7期　2027年 1月28日
+8期　2027年 2月10日
+9期　2027年 3月11日</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>1期　10月23日
+2期　11月13日
+3期　12月4日
+4期　12月4日
+5期　12月11日
+6期　2027年1月8日
+7期　2027年 2月19日
+8期　2027年 3月5日
+9期　2027年 3月17日</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>・出身学校の調査書
+・出願時に提出するテーマ型小論文
+・大学で実施する面接</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>13日</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>芦屋大学</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>環境教育学部　環境教育学科・経営教育学部　経営教育学科</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>5名</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>80%以上</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>【A日程】2026年9月4日（金）～2026年9月18日（金）
 【B日程】2026年11月5日（木）～2026年11月18日（水）
@@ -745,21 +919,21 @@
 ※簡易書留速達郵便</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>【A日程】2026年10月6日（火）
 【B日程】2026年12月2日（水）
 【C日程】2027年2月12日（金）</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>【A日程】2026年10月13日（火）
 【B日程】2026年12月9日（水）
 【C日程】2027年2月19日（金）</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>一次入学手続締切日
 【A日程】2026年10月27日（火）
@@ -771,64 +945,64 @@
 【C日程】2027年3月19日（金）</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>・書類審査
 ・個別面接（日本語の音読を含む）
 20分程度</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>20日</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>神戸医療未来大学</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>【姫路キャンパス】／未来社会学科、経営データビジネス学科、健康スポーツコミュニケーション学科／／【大阪天王寺キャンパス】／経営データビジネス学科</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>【姫路キャンパス】／２名／／【大阪天王寺キャンパス】／1名</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N2相当以上の日本語能力を有する者。</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>N2相当以上の日本語能力を有する者。（N3・N3レベルの試験合格必須）</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>1期）2026年9月14日（月）～2026年9月25日（金）
 2期）2026年10月14日（水）～2026年10月23日（金）
 3期）2026年11月11日（水）～2026年11月19日（木）</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>1期）10月10日（土）10月11日（日）姫路・大阪
 2期）11月7日（土）11月8日（日）姫路・大阪
@@ -836,67 +1010,67 @@
 ※いずれも日付指定不可</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>1期）10月22日（木）
 2期）11月17日（火）
 3期）12月15日（火）</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>1期）10月30日（金）
 2期）11月26日（木）
 3期）12月24日（木）</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>面接試験（６０点）
 書類審査の成績
 （１００点）</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>23日</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>流通科学大学</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>3名</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　9月9日(水)～9月28日(月)
 Ⅱ期　11月9日(月)～11月30日(月)
@@ -904,7 +1078,7 @@
 Ⅳ期　2月1日(月)～2月19日(金)</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　10月17日（土）
 Ⅱ期　12月19日（土）
@@ -912,7 +1086,7 @@
 Ⅳ期　3月10日（水）</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　11月2日（月）
 Ⅱ期　12月25日（金）
@@ -920,7 +1094,7 @@
 Ⅳ期　3月17日（水）</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　1次:11月20日(金)
 　　　2次:1月13日(水)
@@ -929,195 +1103,195 @@
 Ⅳ期　3月23日(火)</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>①書類審査（学校長推薦書及び志望理由書）
 ②面接※指定校推薦入学試験は、日本語（作文）が免除となります。</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>27日</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>京都外国語大学</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>外国語学部　日本語学科／国際貢献学部　グローバルスタディーズ学科・グローバル観光学科</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>3名／(１学科につき　1名)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>N１：110点以上での合格</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/9/24(木)～10/2(金)
 B日程：2026/12/8(火)～12/12(土)</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/10/23(金)
 B日程：2026/12/19(土)</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/11/1(日)
 B日程：2026/12/25(金)</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/11/13(金)
 B日程：2027/1/15(金)</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>・書類選考　
 ・個人面接(15分 オンライン)
 ※面接は外国語学部と国際貢献学部グローバル観光学科は【日本語】で、グローバルスタディーズ学科は【英語】で面接を行う。</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>27日</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>大阪経済法科大学</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>経済学部 経済学科、経営学部 経営学科、法学部 法律学科、国際学部 国際学科</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>前期後期合わせて／計2名／経済学部、経営学部</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>N2以上、またはEJUにおける日本語（読解・聴読解・聴解）が230点以上の者、または、日本語（読解・聴読解・聴解）が200点以上230点未満の者で、下記のいずれ</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>【前期試験】2026年9月24日（木）～10月2日（金）
 【後期試験】2026年12月25日（金）～2027年1月20日（水）</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>【前期試験】2026年10月11日（日）
 【後期試験】2027年2月1日（月）</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>【前期試験】2026年11月2日（月）
 【後期試験】2027年2月12日（金）</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>【前期試験】2026年1月22日（金）
 【後期試験】2027年2月26日（金）</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>志望理由書（600字）
 面接</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>32日</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>大阪観光大学</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>観光学部</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>指定校2名／編入2名</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>N2以上、EJUの日本語得点200点以上、J.TEST600点以上、NAT-TEST2級以上のいずれかを有するもの</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>【指定校推薦】
 A日程：9/7～10/7
@@ -1133,7 +1307,7 @@
 D日程：1/26～2/10</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>【指定校推薦】
 A日程：10/17
@@ -1148,7 +1322,7 @@
 D日程：2/20</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>【指定校推薦】
 A日程：11/2
@@ -1163,7 +1337,7 @@
 D日程：3/2</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>【指定校推薦】
 A日程：11/19
@@ -1178,56 +1352,56 @@
 D日程：3/11</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>書類選考
 個人面談</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>34日</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>名古屋経済大学</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>経済学部現代経済学科、経営学部経営学科、法学部ビジネス法学科</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>N2（B2）レベル相当以上の日本語能力があると認められる者</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　2025年9月30日（水）10:00～10月9日（金）15:00
 Ⅱ期　2025年10月28日（水）10:00～11月4日（水）15:00
@@ -1239,7 +1413,7 @@
 ※出願書類提出は締め切り日当日消印有効</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　10月17日（土）
 Ⅱ期　11月15日（日）
@@ -1249,7 +1423,7 @@
 Ⅵ　3月5日（金）</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　11月2日（月）
 Ⅱ期　12月1日（火）
@@ -1259,7 +1433,7 @@
 Ⅵ期　3月11日（木）</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期　11月19日（木）
 Ⅱ期　12月17日（木）
@@ -1269,7 +1443,7 @@
 Ⅵ期　3月23日（火）</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>書類審査、面接、小論文により、合否を決定します。
 小論文は以下の2題を出題します。解答時間は60分です。
@@ -1278,68 +1452,68 @@
 ②試験当日にテーマ公表、読解作文（200字程度）</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>39日</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科・経済学部 経済学科・／システム工学部 システム工学科</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>9/14(月)～10/14(水)</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>10/24（土）
 集合時間:12:30
 試験時間:13:00</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>11/1（日）
 10:00～</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>（１次）入学金の納入と手続き書類の提出
 11/2（月）～12/1（火）消印有効
@@ -1347,7 +1521,7 @@
 11/2（月）～12/17（木）</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>エントリーシートに基づく面接
 200点
@@ -1355,46 +1529,46 @@
 しかし、入学試験の結果において、大学の授業に支障があると判断した場合、不合格の可能性あり。</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>40日</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>国際日本・建築&amp;芸術・現代社会・経営／／大手前短期大学／ライフデザイン総合</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>N2以上、NAT-TEST2級以上、J-TEST(A-Cレベル600点以上)、JPT 525点以上のいずれか。</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>A日程：2026/10/1(木)～10/15(木)
 B日程：2026/12/14(月)～2027/1/12(火)
@@ -1402,7 +1576,7 @@
 ※消印有効</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>A日程：11/5(木)
 B日程：1/27(水)
@@ -1410,14 +1584,14 @@
 ※試験会場はすべて、西宮夙川キャンパス</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>A日程：11/19(木)
 B日程：2/11(木・祝)
 C日程：3/4(木)</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>入学金納入期日：
 A日程：2025/12/7(月)
@@ -1430,7 +1604,7 @@
 ※詳細は募集要項に記載あり</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>大学
 ①筆記試験 10:00～11:00
@@ -1444,213 +1618,213 @@
 ②個人面接(約15分)</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>41日</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>現代社会学科・放送・メディア映像学科・人間生活学科／（新）デジタルインテリジェンス学科（仮称）</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>各学科／1名／※新学科のみ未定</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>現代社会学科・放送・メディア映像学科・人間生活学科</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>現代社会学部 現代社会学科／人間生活学部 人間生活学科／1名／／現代社会学部 放送・メディア映像学科／3名</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>N2以上取得もしくはEJU270点以上</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>前期:9/7(月)～10/16(金)
 後期:2/1(月)～2/15(月)
 ※必着</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>前期:10/24(土)
 後期:2/19(金)</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>前期:11/2(月)
 後期:2/25(木)</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>前期:11/19(木)
 後期:3/4(木)</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>面接（15分）
 ※読み上げ小テスト含む</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>65日</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>情報学部　情報デザイン学科/グローバル学部　グローバル学科/心理学部　心理学科（神戸山手キャンパス）／教育学部　教育福祉学科/経営学部　経営学科（尼崎キャンパス）</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格している者</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>202610月6日（火）～11月9日（月）
 締切日消印有効</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>11月21日（土）</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>12月1日（火）</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>1次手続き入学金20万円　12月17日（木）
 2次手続き授業料等　2027年1月21日（木）</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>個人面接を実施し、出願書類及び指定校推薦書とあわせて総合判定の上、合否を判定します。
 試験は、日本語による個人面接（20分程度）を、尼崎キャンパスにて対面で行います。</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>66日</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>人文学科、管理栄養学科</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>前期　11/1～11/10
 後期　2/3～2/13</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>前期　11/21
 後期　2/22</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>前期　12/1
 後期　3/3</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>前期：入学金納入→12/11
 前期授業料等納入→6/14
@@ -1658,194 +1832,194 @@
 前期授業料等納入→6/15</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>面接
 （推薦書・志望理由書）を参考にする</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>66日</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>N2以上またはEJU「日本語（記述問題を含む）」230点以上の者(聴読解及び読解で各100点以上、記述30点以上)。</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>2026年11月1日（日）～11月10日（火）
 締切日必着（郵送に限ります。速達　簡易書留で送付します）</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>2026年11月21日（土）
 口頭試問:13:00～</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>2026年12月7日（月）
 13：00～</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>入学金・春学期分学費・諸会費の納付期間2026年12月7日（月）～2027年1月29日（金）</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>日本語による口頭試問　配点100点</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>67日</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>国際学部　日本学科（留学生対象）</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>N2程度の日本語能力を有する者</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>2026/11/2(月)～11/11(水)
 ※必着</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>面接：
 2026/11/20(金)
 ※学校長からの推薦書・調査書及び課題論文をもとに「書類審査」・「面接」により選抜します。</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>2026/12/1(火)
 ※「選考結果通知書」は学校宛てに郵送します。
 本人へは、出願時に登録していただくPost@net のマイページから発表します。</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>【第1次】2026/12/15(水)…入学金
 【第2次】2026/1/20(火)…春学期分納付金と入学手続書類＜必着＞</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>推薦書・調査書及び課題論文をもとに
 「書類審査」・「面接」により選抜</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>68日</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>1期：11月2日(月)～11月12日(木)
 Ⅱ期：12月1日(火)～12月16日(水)
@@ -1854,7 +2028,7 @@
 Ⅴ期：2月24日(水)～3月11日(木)</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月14日(土)
 Ⅱ期：12月19日(土)
@@ -1863,7 +2037,7 @@
 Ⅴ期：3月13日(土)</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月18日(水)
 Ⅱ期：12月23日(水)
@@ -1872,7 +2046,7 @@
 Ⅴ期：3月18日(木)</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：11月26日(木)
 Ⅱ期：1月7日(木)
@@ -1881,56 +2055,56 @@
 Ⅴ期：3月26日(金)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>・書類審査
 ・個人面接(日本語の口頭試問含むオンライン試験)</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>83日</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>経営学部 経営学科</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>N2以上に合格した者、または、EJU(日本語/記述除く)200点以上の者。</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>85%以上</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年11月9日(月)～11月27日(金)
 (WEB出願は24日の午後5時まで)
@@ -1941,21 +2115,21 @@
 いずれも必着締め切り</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月5日(土)
 Ⅱ期：2027年2月7日(日)
 Ⅲ期：2027年2月26日(金)</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2026年12月11日(金)
 Ⅱ期：2027年2月12日(金)
 Ⅲ期：2027年3月5日(金)</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Ⅰ期：2027年1月13日(水)
 Ⅱ期：2027年2月26日(金)
@@ -1963,56 +2137,56 @@
 必着締め切り</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>①出願書類審査(志望理由書、在籍校での成績及び出席率、推薦書を含む)
 ②面接試験(15分)…集団面接</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>86日</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>経済経営学科、国際文化ビジネス・観光学科</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>N2相当であるもの（※N2相当は下記いずれかの基準）</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 【前期】
@@ -2025,21 +2199,21 @@
 窓口の場合は16:00まで</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/13
 後期：2/22</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期：12/24
 後期：3/4</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>★1年次入学・編入　日程同じ
 前期
@@ -2050,74 +2224,74 @@
 （第二次）〃</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>書類審査
 本学独自の日本語能力試験
 面接</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>96日</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>国際教養学部 英語・国際文化学科、／社会学部 社会学科/社会福祉学科(※現：ソーシャルデザイン学科で2027年4月に社会福祉学科に名称変更構想中)、／法学部 法律学科、経済学部 経済学科、経営学部 経営学科、工学部 工学科</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>N2レベル以上の者、またはEJUの日本語科目(読解、聴解及び聴読解)の得点が220点以上の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>2026年12月1日(火)～12月10日(木)
 ※入学検定料は締め切り12/11(金)13時振込完了
 締切日当日消印有効</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>2026/12/19（土）</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>2026/12/24（木）</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>2026年12月24日(木)～
 2027年2月12日(金)
@@ -2125,7 +2299,7 @@
 入学申込金、春学期授業料一括納入</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>・面接
 ・小論文
@@ -2133,120 +2307,120 @@
 (EJUの成績確認書またはN２以上の成績証明書)/工学部工学科のみEJUの数学コース2及び理科の成績確認書も</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>◇</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>11日</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>追手門学院大学（パートナー校制度）</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>国際学部 国際学科 グローバルスタディーズ専攻</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>【前期】2026年9月10日（木）～2026年9月16日（水）
 【後期】2026年12月18日（金）～2027年1月12日（火）
 ※当日消印有効</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>前期：2026年10月3日（土）
 後期：2027年1月28日（木）</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>【前期】2026年10月9日（金）
 【後期】2027年2月18日（木）</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>【前期】2026年11月9日（月）
 【後期】2027年2月26日（金）</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>筆記試験（日本語読解・小論文）
 面接（日本語・英語）</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>条件卡：需先取得英语成绩证书之一（TOEIC800／IELTS5.5／TOEFL iBT74／Duolingo100）。最快路径 Duolingo English Test（在家考、48小时出分、出分后可选择不发送）。拿到成绩即为全池唯一非专愿紫卡，且按英语能力最高100%学费免除</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>26日</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>太成学院大学</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>健康スポーツ学科、看護学科／心理カウンセリング学科、現代ビジネス学科</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr"/>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr"/>
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>N2（112点以上）またはN1</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>A日程：8/24-9/3
 B日程：9/14-10/1
@@ -2254,7 +2428,7 @@
 D日程：1/4-1/28</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>A日程：9/13
 B日程：10/10
@@ -2262,7 +2436,7 @@
 D日程：2/5</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>A日程：9/18
 B日程：10/16
@@ -2270,7 +2444,7 @@
 D日程：2/12</t>
         </is>
       </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>A日程:
 入学金10/2
@@ -2290,75 +2464,75 @@
 2回目3/16</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr">
+      <c r="M24" s="12" t="inlineStr">
         <is>
           <t>面接
 書類</t>
         </is>
       </c>
-      <c r="N22" s="12" t="inlineStr">
+      <c r="N24" s="12" t="inlineStr">
         <is>
           <t>要求 N2 112 分以上，你 111 分差 1 分（EJU220／JPT525／J.TEST C级600 也可以替代）</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>26日</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>日本工業大学</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr"/>
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>第１期：2026年9月1日（火）～10月1日（木）必着
 第2期：2026年12月10日(木)～2027年1月19日(火)必着</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>第１期：2026年10月11日（日）
 第２期：2027年1月29日(金)
 場所：日本工業大学埼玉キャンパス</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr">
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>第１期：2026年11月2日（月）
 第2期：2027年2月8日(月)</t>
         </is>
       </c>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="L25" s="12" t="inlineStr">
         <is>
           <t>入学金納入
 第1期：2026年11月17日（火）
@@ -2368,132 +2542,132 @@
 第2期：2027年3月9日(火)</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr">
+      <c r="M25" s="12" t="inlineStr">
         <is>
           <t>・書類審査（出席・成績証明書、志望理由書、日本留学試験の受験票）
 ・個人面接(15分)。</t>
         </is>
       </c>
-      <c r="N23" s="12" t="inlineStr">
+      <c r="N25" s="12" t="inlineStr">
         <is>
           <t>必须有 EJU（日语230分，还要考数学课程2）。不认 JLPT</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>27日</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>平安女学院大学</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>国際観光学部　国際観光学科</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>N2以上に合格した方。</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>1期：2026年9/21(月)～10/2(金)
 2期：2027年1/25(月)～2/8(月)</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>1期：2026年10/11(日)13:30～
 2期：2027年2/14(日)13:30～</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr">
+      <c r="K26" s="12" t="inlineStr">
         <is>
           <t>1期：2026年10/16(金)
 2期：2027年2/19(金)</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>1期：2026年12/4(金)
 2期：2027年3/12(金)</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr">
+      <c r="M26" s="12" t="inlineStr">
         <is>
           <t>面接</t>
         </is>
       </c>
-      <c r="N24" s="12" t="inlineStr">
+      <c r="N26" s="12" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>32日</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>園田学園大学</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>経営学部　ビジネス学科</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>5名／5名を超える場合は要相談</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr"/>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr"/>
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>Ⅰ期　9月28日（月）～10月7日（水）
 Ⅱ期　11月24日（火）～12月9日（水）
@@ -2501,7 +2675,7 @@
 Ⅳ期　2月15日（月）～3月2日（火）</t>
         </is>
       </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>Ⅰ期　10月18日（日）10：00
 Ⅱ期　12月20日（日）10：00
@@ -2509,7 +2683,7 @@
 Ⅳ期　3月9日（火）10：00</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="K27" s="12" t="inlineStr">
         <is>
           <t>Ⅰ期　10月23日（金）
 Ⅱ期　12月24日（木）
@@ -2517,66 +2691,66 @@
 Ⅳ期　3月12日（金）</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L27" s="12" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr">
+      <c r="M27" s="12" t="inlineStr">
         <is>
           <t>書類
 面接(10分　100点)
 小論文（10分　100点）</t>
         </is>
       </c>
-      <c r="N25" s="12" t="inlineStr">
+      <c r="N27" s="12" t="inlineStr">
         <is>
           <t>女子大学实质（2025年4月才由园田学园女子大学改制共学，在校生构成仍是女子大延续）——按你的短大·女大指定排除</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>38日</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>駒沢女子大学・短期大学</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>国際日本語学科・人間関係学科・心理学科・観光文化学科・空間デザイン学科</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>N2相当の者</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>※入学検定料振込：10:00～15:00
 ※必要書類郵送：最終日消印有効
@@ -2588,7 +2762,7 @@
 Ⅲ₋b期：2/18(木)～2/25(木)</t>
         </is>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>Ⅰ₋a期：10/24(土)
 Ⅰ₋b期：11/21(土)
@@ -2598,7 +2772,7 @@
 Ⅲ₋b期：3/10(水)</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>Ⅰ₋a期：11/2(月)
 Ⅰ₋b期：12/1(火)
@@ -2608,158 +2782,245 @@
 Ⅲ₋b期：3/12(金)</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L28" s="12" t="inlineStr">
         <is>
           <t>‐</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr">
+      <c r="M28" s="12" t="inlineStr">
         <is>
           <t>面接（15分程度）
 書類審査</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr">
+      <c r="N28" s="12" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>38日</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>城西国際大学</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>国際人文学部 国際文化学科/国際交流学科／観光学部 観光学科、経営情報学部 総合経営学科(総合経営コース)／メディア学部 メディア情報学科(ニューメディアコース)、健康科学部 福祉総合学科</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>専願</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>N2以上を取得した者。取得していない場合は以下の基準を満たす者</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>85%以上</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>【1期】
+インターネット出願登録期間：9月7日～10月13日
+出願期間(書類提出期間)：9月29日～10月14日必着
+【2期】
+インターネット出願登録期間：10月9日～11月24日
+出願期間(書類提出期間)：11月10日～11月25日必着
+【3期】
+インターネット出願登録期間：12月18日～2027年1月31日
+出願期間(書類提出期間)：2027年1月13日～2月2日必着</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>【1期】10月31日(土)
+【2期】12月12日(土)
+【3期】2027年2月19日(金)</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>【1期】11月10日(火)
+【2期】12月22日(火)
+【3期】2027年3月2日(火)</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>【1期】11月24日(火)
+【2期】2027年 1月6日(水)
+【3期】2027年 3月11日(木)</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>・面接
+・書類審査(小論文の評価を含む)</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>学校指定校名单上该校条件栏为空、日程未记载（标注「編集中」）＝当前不存在可执行的出愿路径。（大学官网2026定价138.7万可查，但指定校条件未发布前无法出愿）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>40日</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>大阪国際大学</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>経営経済学部 経営学科/経済学科、／国際教養学部 国際コミュニケーション学科/国際観光学科</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>各1名ずつ</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>2026年10月5日～10月15日
 （消印有効）</t>
         </is>
       </c>
-      <c r="J27" s="12" t="inlineStr">
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>2026-10-24 00:00:00</t>
         </is>
       </c>
-      <c r="K27" s="12" t="inlineStr">
+      <c r="K30" s="12" t="inlineStr">
         <is>
           <t>2026-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>入学金〆切：11月6日～11月20日
 前期学費納入〆切：11月6日～12月18日</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr">
+      <c r="M30" s="12" t="inlineStr">
         <is>
           <t>書類選考
 面接</t>
         </is>
       </c>
-      <c r="N27" s="12" t="inlineStr">
+      <c r="N30" s="12" t="inlineStr">
         <is>
           <t>必须有 EJU（日语200分）。不认 JLPT</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>131日</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>近畿大学</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>国際学部国際学科グローバル専攻</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>前期・後期合計／2名</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>【前期】2026年8月24日（月）～8月27日（木）
 【後期】2027年1月8日（金）～1月14日（木）</t>
         </is>
       </c>
-      <c r="J28" s="12" t="inlineStr">
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>【前期試験】2026年10月10日（土）
 【後期試験】2027年2月20日（土）</t>
         </is>
       </c>
-      <c r="K28" s="12" t="inlineStr">
+      <c r="K31" s="12" t="inlineStr">
         <is>
           <t>【前期試験】2026年11月9日（月）
 【後期試験】2027年3月9日（火）</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L31" s="12" t="inlineStr">
         <is>
           <t>【前期試験】
 第一次手続：2026年11月9日（月）～11月27日（金）
@@ -2767,207 +3028,207 @@
 【後期試験】2027年3月9日（火）～3月15日（月）</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr">
+      <c r="M31" s="12" t="inlineStr">
         <is>
           <t>口頭試問、日本留学試験成績
 総合して合否を判定</t>
         </is>
       </c>
-      <c r="N28" s="12" t="inlineStr">
+      <c r="N31" s="12" t="inlineStr">
         <is>
           <t>必须有 EJU（日语300分＋综合科目100分＋总分400分）。不认 JLPT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>131日</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>神戸学院大学</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>グローバル・コミュニケーション学部　グローバル・コミュニケーション学科日本語コース</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
         <is>
           <t>2027年1月6日（水）～1月14日（木）必着</t>
         </is>
       </c>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>2月10日（水）</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>2月19日（金）</t>
         </is>
       </c>
-      <c r="L29" s="12" t="inlineStr">
+      <c r="L32" s="12" t="inlineStr">
         <is>
           <t>第1次:2月22日（月）～3月1日（月）厳守
 第2次:2月22日（月）～3月8日（月）厳守</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr">
+      <c r="M32" s="12" t="inlineStr">
         <is>
           <t>・書類選考
 ・面接
 13:10～</t>
         </is>
       </c>
-      <c r="N29" s="12" t="inlineStr">
+      <c r="N32" s="12" t="inlineStr">
         <is>
           <t>必须有 EJU（日语240分）。不认 JLPT</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>上海大学</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>中国語学部中国語学科</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>日本語要件の記載なし</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>95%以上</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>2026年5月1日～出願終了まで</t>
         </is>
       </c>
-      <c r="J30" s="12" t="inlineStr">
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="K30" s="12" t="inlineStr">
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L33" s="12" t="inlineStr">
         <is>
           <t>指定校あてに通知</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr">
+      <c r="M33" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="N30" s="12" t="inlineStr">
+      <c r="N33" s="12" t="inlineStr">
         <is>
           <t>要求中国籍以外，你不符合</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>中日本自動車短期大学（岐阜）</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>自動車工学科(2年)・モータースポーツエンジニアリング学科(3年)</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>N2程度の日本語能力を有する者。</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>10月期　9月10日-17日
 11月期　10月15日-22日
@@ -2975,7 +3236,7 @@
 2月期　1月15日-22日</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>10月期　10月11日
 11月期　11月15日
@@ -2983,7 +3244,7 @@
 2月期　2月7日</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K34" s="12" t="inlineStr">
         <is>
           <t>10月期　10月19日
 11月期　11月23日
@@ -2991,7 +3252,7 @@
 2月期　2月15日</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L34" s="12" t="inlineStr">
         <is>
           <t>1次
 10月期　11月13日
@@ -3001,59 +3262,59 @@
 (2次は全て3月15日）</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr">
+      <c r="M34" s="12" t="inlineStr">
         <is>
           <t>面接・書類審査</t>
         </is>
       </c>
-      <c r="N31" s="12" t="inlineStr">
+      <c r="N34" s="12" t="inlineStr">
         <is>
           <t>短期大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>大阪女学院大学</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>大阪女学院大学（3年次編入学）／大阪女学院短期大学／／国際教養学部　国際教養学科</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>N2以上</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>共通
 一期：9/24(木)∼9/30(水)
@@ -3064,7 +3325,7 @@
 六期：2027/3/3(水)∼3/9(火)</t>
         </is>
       </c>
-      <c r="J32" s="12" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>共通
 一期：10/11(日)
@@ -3075,7 +3336,7 @@
 六期：2026/3/17(水)</t>
         </is>
       </c>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>共通
 一期：10/16(金)
@@ -3086,7 +3347,7 @@
 六期：2027/3/17(水)</t>
         </is>
       </c>
-      <c r="L32" s="12" t="inlineStr">
+      <c r="L35" s="12" t="inlineStr">
         <is>
           <t>入学金(100,000円納入　書類提出期日)
 一期：11/2(月)
@@ -3104,61 +3365,61 @@
 六期：2025/3/27(火)</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr">
+      <c r="M35" s="12" t="inlineStr">
         <is>
           <t>共通
 面接(日本語)約20分
 ※うち3分程度で「日本語と英語をどのように勉強してきたのか、また入学後どのように勉強したいのか」を日本語で発表</t>
         </is>
       </c>
-      <c r="N32" s="12" t="inlineStr">
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>女子大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>大阪キリスト教短期大学</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>①介護福祉別科／②教育テックコースDXグローバルクラス</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>介護福祉別科：2名／教育テック：3名</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>専願</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>N2 相当またはCEFR B2 以上の日本語力の習得を目指す意志のある者</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>90%以上</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年8月7日(金)～8月21日(金)
@@ -3166,7 +3427,7 @@
 2026年8月3日(月)～2026年8月17日(月)</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年8月29日(土)
@@ -3174,7 +3435,7 @@
 8月29日（土）</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="K36" s="12" t="inlineStr">
         <is>
           <t>【介護福祉別科】
 2026年9月11日(金)
@@ -3182,12 +3443,12 @@
 9月14日（月）</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L36" s="12" t="inlineStr">
         <is>
           <t>記載なし</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
+      <c r="M36" s="12" t="inlineStr">
         <is>
           <t>【介護福祉学科】
 書類審査
@@ -3202,58 +3463,14 @@
 日本語での面接を実施</t>
         </is>
       </c>
-      <c r="N33" s="12" t="inlineStr">
+      <c r="N36" s="12" t="inlineStr">
         <is>
           <t>短期大学（你指定排除）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>城西国際大学</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>国際人文学部 国際文化学科/国際交流学科／観光学部 観光学科、経営情報学部 総合経営学科(総合経営コース)／メディア学部 メディア情報学科(ニューメディアコース)、健康科学部 福祉総合学科</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr"/>
-      <c r="G34" s="12" t="inlineStr"/>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>記載なし</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr"/>
-      <c r="J34" s="12" t="inlineStr"/>
-      <c r="K34" s="12" t="inlineStr"/>
-      <c r="L34" s="12" t="inlineStr"/>
-      <c r="M34" s="12" t="inlineStr"/>
-      <c r="N34" s="12" t="inlineStr">
-        <is>
-          <t>学校指定校名单上该校条件栏为空、日程未记载（标注「編集中」）＝当前不存在可执行的出愿路径。（大学官网2026定价138.7万可查，但指定校条件未发布前无法出愿）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N34"/>
+  <autoFilter ref="A1:N36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3264,7 +3481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3334,15 +3551,90 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
+          <t>愛知産業大学</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>複数名</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>【推薦基準】
+以下の(ア)～(エ)のいずれかを満たす者で入学を強く希望する者(専願)
+ただし、(ウ)については日本語教育機関での出席率が90%以上の者に限る。
+(ア)EJUの「日本語(読解、聴解及び聴読解の合計)」が200点以上(受験年度は問わないが、公式に発行された成績であること)
+(イ)JLPT N2以上に合格している者
+(ウ)日本語学校において、通算600時間以上の日本語学習歴を有すること。
+(エ)文部科学省が示している「日本語教育の参照枠」B2以上相当の者、その他(ア)～(ウ)と同等以上の日本語能力を有すると本学が認めた者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>大阪人間科学大学</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>【外国人留学生当別推薦入試】
+推薦基準：
+１．令和9年(2027年)３月卒業見込み
+２．JLPT N2またはJPT 525点以上、CEFR B2以上、EJU 200点以上と同程度の能力を有する者（N2を満たさない者は入試広報センターへ申し出ること）
+３．出席率90％以上
+出願資格：
+次の１，２のいずれかに該当し、３～６を充たす者(専願)
+１．外国籍を有し、外国において学校教育における12年の課程を修了した者、もしくはこれに準ずる者として文部科学大臣の指定した者
+２．本学において上記１に準ずると認めた者（事前に認定審査を行うので出願期間開始日の1か月前までに入試広報センターへ申し出ること）
+３．「出入国管理及び難民認定法」による大学入学に支障のない在留資格「留学」を有する者
+４．令和9年(2027年)４月1日現在において満１８歳に達する者
+５．本学のアドミッションポリシーを十分に理解している者
+６．合格すれば必ず本学へ入学する者
+※オープンキャンパス参加者の検定料減額制度について：
+インターネット出願時に、オープンキャンパス当日に配布する「オープンキャンパス参加者検定料減額制度番号」を入力して出願すると、検定料を5,000円減額する。
+【3年次編入学試験】
+推薦基準：
+「外国人留学生特別推薦入試」と同じ
+出願資格：
+・外国での学歴12年(無い者は、大学で認定審査を行うため出願期間開始日の1か月前までに入試広報センターへ申し出ること)
+・「出入国管理及び難民認定法」による大学入学に支障のない在留資格「留学」を有する者
+・令和9年(2027年)４月1日現在において満１８歳に達する者
+・本学のアドミッションポリシーを十分に理解している者
+・合格すれば必ず本学へ入学する者
+※オープンキャンパス参加者の検定料減額制度について：
+インターネット出願時に、オープンキャンパス当日に配布する「オープンキャンパス参加者検定料減額制度番号」を入力して出願すると、検定料を5,000円減額する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
           <t>芦屋大学</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>5名</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>推薦条件
 ①大学生活に支障のない経済状況にある者
@@ -3355,23 +3647,23 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>神戸医療未来大学</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>【姫路キャンパス】／２名／／【大阪天王寺キャンパス】／1名</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>【出願資格】(1～3のいずれかに該当する者)
 (１)外国籍を有し、2027年4月までに18歳に達する者で、本学での授業に支障のない程度(日本語教育の参照枠でB２相当以上)の日本語能力を有すると認められる者。
@@ -3381,28 +3673,28 @@
 【推薦条件】
 ①指定する学校の学校長の推薦を得られる者。
 ②出席率が95％以上であること。（両キャンパス共に）
-③JLPT・N2相当以上の日本語能力を有する者。
+③JLPT・N2相当以上の日本語能力を有する者。（N3・N3レベルの試験合格必須）
 ④本学を専願とすること。</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>流通科学大学</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>3名</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>出願資格　
 2027年度外国人留学生入試の出願資格に該当し、本学が指定する日本語学校等を2027年3月に卒業見込みの者で、本学を専願とする者。
@@ -3415,23 +3707,23 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>京都外国語大学</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>3名／(１学科につき　1名)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>【各学科共通】
 (1)から(7）のすべてに該当する者
@@ -3464,23 +3756,23 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>大阪経済法科大学</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>前期後期合わせて／計2名／経済学部、経営学部</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>①専願する者
 ②JLPTN2以上、またはEJUにおける日本語（読解・聴読解・聴解）が230点以上の者、または、日本語（読解・聴読解・聴解）が200点以上230点未満の者で、下記のいずれかのスコアを取得している者。
@@ -3490,23 +3782,23 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>大阪観光大学</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>指定校2名／編入2名</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>①2027年3月卒業見込みで、学校長が推薦したもの。
 ②出席率が90％以上のもの。
@@ -3515,23 +3807,23 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>名古屋経済大学</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>外国籍を有する者で、次の（1）～（5）のすべてに該当する者、または（2）～（6）のすべてに該当する者とする。
 （1）外国において、学校教育における12年の課程を修了した者、もしくはこれに準ずる者で文部科学大臣のしてした者、または高等学校を卒業した者と同等以上の学力があると本学が認めた者
@@ -3543,23 +3835,23 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>大阪産業大学</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>経営学部　経営学科→商学コース　1名／経済学部　経済学科→経済学コース　1名／システム工学部　システム工学科　1名</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>①日本国籍を有しない者
 ②下記（1）～（3）のいずれかを満たす者
@@ -3575,23 +3867,23 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>大手前大学</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>【大学・短大共通条件↓】
 出席率90%以上
@@ -3617,23 +3909,23 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>羽衣国際大学</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>各学科／1名／※新学科のみ未定</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>現代社会学部 現代社会学科／人間生活学部 人間生活学科／1名／／現代社会学部 放送・メディア映像学科／3名</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>出願資格：次の各項のすべてに該当する者
 ①貴校の校長が推薦し、かつ本学を専願とする者
@@ -3655,23 +3947,23 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>関西国際大学</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>全学部合計4名</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>出願資格
 外国籍を有する者で、（1）出願資格のいずれかに該当し、かつ（2）出願条件と（3）（4）を満たし、本学を専願とする者に出願資格があります。
@@ -3691,23 +3983,23 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>相愛大学</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>各学科／前期：5名／後期：若干名</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>【人文学科】
 １～６すべてに該当し、かつ学業・人物について学校長の推薦を受けた専願者に限る
@@ -3734,23 +4026,23 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>大阪経済大学　国際共創部　国際共創学科</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>①外国の国籍を有し、外国において学校教育における12年の課程を修了した者、もしくは2027年3月までに修了見込みの者
 ※12年の課程のうち、日本の高等学校での在籍期間が3年以内の者も資格を有する。
@@ -3763,23 +4055,23 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>天理大学</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>出願資格：
 つぎの１から５のいずれかにも該当する者。
@@ -3792,23 +4084,23 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>育英館大学</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>出願資格
 ①～⑤のすべてを満たす者
@@ -3822,23 +4114,23 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>山梨学院大学</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>【推薦条件】
 ①本学の入学者選抜に合格した場合、入学意思がある者(専願)
@@ -3852,23 +4144,23 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>神戸国際大学</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>（1年入学）各学科1名／（2年編入）1名</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>次の条件を満たすもの
 【1年次入学】
@@ -3900,23 +4192,23 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>桃山学院大学</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>6名</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>【出願資格】以下の全てに該当する者
 (1)日本居住の外国人で、外国において12年の学校教育を修了した者。
@@ -3926,23 +4218,23 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>◇</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>追手門学院大学（パートナー校制度）</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>【前期】
 ・JLPT N3以上
@@ -3962,23 +4254,23 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>太成学院大学</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>１)下記の試験・スコアのいずれか一つ以上を有している方
 ・日本留学試験（EJU）＿220点以上
@@ -3989,23 +4281,23 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>日本工業大学</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>出願条件：
 ①外国籍を有し、外国において学校教育における12年の課程を修了した方、またはこれに準ずる文部科学大臣の指定した方。
@@ -4020,23 +4312,23 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>平安女学院大学</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>1名</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>（1）本学指定する日本語教育施設で、在籍する学校長の推薦を受けた方。
 （2）外国において学校教育における12年の課程を修了した方、文化科学省が定める大学入学資格に該当する方、または本学においてこれと同等以上の資格を有すると認められる方。
@@ -4048,46 +4340,46 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>園田学園大学</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>5名／5名を超える場合は要相談</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>①授業時間600時間を満たした者かつ、日本語教育の参照枠におけるB2以上の日本語能力を有する者
 ②出席率90％以上</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>駒沢女子大学・短期大学</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>（１）2027年3月に貴校を卒業見込みの者で、人間性に富み、高等教育を受けるのに適した素質と必要な学力をもち学校長が推薦するに値すると認めた者。
 （２）本学への入学を第一希望とし、合格した場合は必ず入学する者（専願）
@@ -4099,23 +4391,59 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>城西国際大学</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>若干名</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>【出願資格】
+・専願
+・日本語でのコミュニケーション能力に問題がなく、学校長の推薦を得られる者。
+・授業の出席率が85%以上
+・日本語能力において下記の(１)～(７)のいずれか1つに該当する者
+(１)JLPT N2以上を取得した者。取得していない場合は以下の基準を満たす者
+　　ア.N2不合格の場合は、総合得点80点以上で、各得点区分の基準点(19点)以上。
+　　イ.N1不合格の場合は、総合得点90点以上で各得点区分の基準点(19点)以上。
+(２)EJUにおいて「日本語」科目を受験し、200点以上を取得した者。
+　　(「読解」及び「聴解・聴読解」の合計点で計算し、「記述」は得点に含めない。過去2年までの成績が有効)
+(３)日本語NAT-TEST2級以上を取得した者(過去2年までの成績が有効)
+(４)J.TESTのA-Cレベル600点以上を取得した者(過去2年までの成績が有効)
+(５)BJTビジネス日本語能力テスト400点以上(過去2年までの成績が有効)
+(６)J-CAT250点以上(ただし、各得点区分で30点を下回らないこと。過去2年までの成績が有効)
+(７)JPT日本語能力試験525点以上を取得した者(過去2年までの成績が有効)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>大阪国際大学</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>各1名ずつ</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D30" s="18" t="inlineStr">
         <is>
           <t>【出願資格】
 ①2027年3月に日本語学校を修了見込みのもの
@@ -4127,23 +4455,23 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>近畿大学</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>前期・後期合計／2名</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>下記①～③のいずれかを満たす者
 ①外国に所在する学校で所在国・地域の法令に基づく正規の学校教育における12年目の課程を修了した者または2027年3月までに修了見込みの者
@@ -4157,23 +4485,23 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>神戸学院大学</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>１名</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>被推薦者の資格
 ①外国において学校教育における12年の課程を修了した者、または、これに準ずる者で文部科学大臣の指定した者。
@@ -4187,23 +4515,23 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>上海大学</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>①募集要項に記載の出願資格を満たしている者
 ・高等学校卒業まはたそれに相当する資格を有すること
@@ -4217,23 +4545,23 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>中日本自動車短期大学（岐阜）</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>2名</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>以下の条件を全て満たしていること
 ・入国管理及び難民認定法の定めるところにより、在留資格「留学」を有するもの及び取得見込みの者。（技能実習ビザのものは不可）
@@ -4252,23 +4580,23 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>大阪女学院大学</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>若干名</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>●推薦条件（大阪女学院大学・大阪女学院短期大学）
 １）日本語学校用の学校長の推薦を受け、本学で学ぶ意欲のある専願の方
@@ -4290,23 +4618,23 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>大阪キリスト教短期大学</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>介護福祉別科：2名／教育テック：3名</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
         <is>
           <t>以下の条件を満たす者↓
 【介護福祉学科】
@@ -4326,24 +4654,6 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>城西国際大学</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>若干名</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
